--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="Rf670459e39794e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="R26b31e33be9c4d5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -549,10 +549,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Стеновые панели Adamar </x:v>
+        <x:v>Гибкий мрамор 114×280 см — WHITE CONCRETE</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Стеновые панели Adamar Group: гибкий мрамор, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «WHITE CONCRETE». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K2" t="str">
         <x:v>Новое</x:v>
@@ -668,10 +668,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Дуб Сонома</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Дуб Сонома». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K3" t="str">
         <x:v>Новое</x:v>
@@ -787,10 +787,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — White Concrete Fon</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «White Concrete Fon». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K4" t="str">
         <x:v>Новое</x:v>
@@ -906,10 +906,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Grey Lord</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Grey Lord». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K5" t="str">
         <x:v>Новое</x:v>
@@ -1025,10 +1025,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I6" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — White Rock</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «White Rock». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K6" t="str">
         <x:v>Новое</x:v>
@@ -1144,10 +1144,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Орех тёмный</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Орех тёмный». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K7" t="str">
         <x:v>Новое</x:v>
@@ -1263,10 +1263,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I8" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Scandi</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Scandi». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>Новое</x:v>
@@ -1382,10 +1382,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Дуб Винтаж</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Дуб Винтаж». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>Новое</x:v>
@@ -1501,10 +1501,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I10" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Beige Concrete</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Beige Concrete». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>Новое</x:v>
@@ -1620,10 +1620,10 @@
         <x:v>Отделка</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Гибкий мрамор для стен,</x:v>
+        <x:v>Гибкий мрамор 114×280 см — Terrazzo White</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Гибкий мрамор для стен, 1140х2800 мм». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
+        <x:v>Гибкий мрамор для стен 114×280 см, декор «Terrazzo White». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Монтаж на сухое, чистое и прочное основание. В душевой герметизируйте стыки и примыкания.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>Новое</x:v>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="Rf4737d64329748f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="R075e0d158e6d4737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Re8bface413944a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R385f1c0706314c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="Re344d806b7654e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Rfd8881d1dc88477a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Instructions" localSheetId="0">Инструкция!$1:$50</x:definedName>
@@ -1800,13 +1800,13 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R070d5c52a71c4dc0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="Rea060320cc6c4a58"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R4fd32b83f37849bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="R74700a2ac4914046"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R9b6811275b1a414b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="Rb88e6ea5fad846e5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="R0057017a2c3646bf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R3cd69109f5814563"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R982382289f284cfc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="Rf3bd5380485342c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="Rfec412531e664a85"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R266f0e9fe1f74591"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="R67332dc538894310"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="R40ba34d2bc094c0d"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2405,7 +2405,16 @@
         <x:v>Гибкий мрамор 114×280 см — WHITE CONCRETE</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «WHITE CONCRETE». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «WHITE CONCRETE» — Светлый бетонный рисунок выглядит современно и не перегружает интерьер — хороший фон для минимализма, лофта и спокойных светлых пространств. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K5" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/hzcnmmgxsdvr4ml8wdnjqmffft5jhjtc/orig | https://avatars.mds.yandex.net/get-yastore/21044143/r4bpdkc7m46nn5nx2brwptjdqctlhk7t/orig | https://avatars.mds.yandex.net/get-yastore/21044143/dsfdgrdk2k2q2hvk56cf8v2g2z8kw4bb/orig | https://avatars.mds.yandex.net/get-yastore/20274467/dd25xxsshglhg7tztjqg92qhnc5f9g7r/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
@@ -2521,7 +2530,16 @@
         <x:v>Гибкий мрамор 114×280 см — Дуб Сонома</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Дуб Сонома». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Дуб Сонома» — Тёплая древесная фактура добавляет интерьеру уюта и хорошо сочетается со светлой мебелью, спокойными стенами и натуральными оттенками. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K6" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/18919159/p7r2b4mtds77d6lzdjz6ksgbcd9kgcx9/orig | https://avatars.mds.yandex.net/get-yastore/18919159/m8dvrkghm7lh2jpg5v76928tc56xbllp/orig | https://avatars.mds.yandex.net/get-yastore/21598990/nm66rkbzrndqsp86grkbf5w6rqlfpp27/orig | https://avatars.mds.yandex.net/get-yastore/19034732/9vf677trzvspc2bpjpbhzgv6ph79w6sf/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bdz5sbrvkr2z6wxw626w5jrxx6shbvwq/orig</x:v>
@@ -2637,7 +2655,16 @@
         <x:v>Гибкий мрамор 114×280 см — White Concrete Fon</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «White Concrete Fon». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «White Concrete Fon» — Мягкий светлый бетон создаёт аккуратный нейтральный фон и визуально делает пространство легче — особенно удачно смотрится в кухне и ванной. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K7" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jxvfhrwn5qgx4v29kj74p2wknsjtqjl5/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xmsrjq5wl6dpz7gq6v98f4vcwxvc692s/orig | https://avatars.mds.yandex.net/get-yastore/20760651/x8lfdrwhmtgbsnqkbj5cb6chhvvntlwl/orig | https://avatars.mds.yandex.net/get-yastore/20760651/87jmpptxgkltrl79k95488prdfqjn2w6/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
@@ -2753,7 +2780,16 @@
         <x:v>Гибкий мрамор 114×280 см — Grey Lord</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Grey Lord». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Grey Lord» — Выразительный серый камень помогает собрать строгий современный интерьер и подходит для акцентной стены без лишней пестроты. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/zchqpmj7gl7k4c5lz72mxv5cr8n6mms7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4pznjgzkm2wf9qbtrbz4xfn7hg8mhm4j/orig | https://avatars.mds.yandex.net/get-yastore/20918687/7l568nzcwmdvm6jwwgd7srnfxvl8c6p8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/4qvg5mb65w8ptttxbbj8qch54784c4d5/orig</x:v>
@@ -2869,7 +2905,16 @@
         <x:v>Гибкий мрамор 114×280 см — White Rock</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «White Rock». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «White Rock» — Светлая каменная текстура освежает помещение и даёт эффект цельной дорогой отделки, сохраняя спокойную цветовую гамму. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20811730/cqpzstj9nzd8wrbprll9frnrl6x9g4wp/orig | https://avatars.mds.yandex.net/get-yastore/21497181/nwc5cp78n76vn97z555g2zlbvfmf22kl/orig | https://avatars.mds.yandex.net/get-yastore/21598990/6cxjqfncddsz5hcd72mb8mc7nlplxd5h/orig | https://avatars.mds.yandex.net/get-yastore/19034732/s67p8kgt597xq9kzwvdhs9x4k4knk4b5/orig | https://avatars.mds.yandex.net/get-yastore/19034732/d95z2nt8lmf8rvq68qtgvmvdskjnj665/orig</x:v>
@@ -2985,7 +3030,16 @@
         <x:v>Гибкий мрамор 114×280 см — Орех тёмный</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Орех тёмный». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Орех тёмный» — Глубокий древесный оттенок делает интерьер теплее и солиднее — красивое решение для кабинета, спальни, прихожей или акцентной стены. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21580234/kqljphlmrr8v4ftp5q7fgnc7m2x6mwxg/orig | https://avatars.mds.yandex.net/get-yastore/20811730/z2jfrv44x46kw2xnqxjdmcjlkjjkc7qt/orig | https://avatars.mds.yandex.net/get-yastore/19782553/gqwpd5z6k62dbtwxtm4dptjtf2jmqpdz/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bvccxxtwvgdx2f6l9vjgxn94s2jrzrwk/orig</x:v>
@@ -3101,7 +3155,16 @@
         <x:v>Гибкий мрамор 114×280 см — Scandi</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Scandi». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Scandi» — Лёгкий скандинавский рисунок поддерживает светлый интерьер, добавляет естественную фактуру и хорошо работает в небольших помещениях. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/9hcv6xhdxnfjrwwd98qg92wl4v5lgz6f/orig | https://avatars.mds.yandex.net/get-yastore/20274467/jsx9k6l9fsmls57rbgv52zbzcrt5zwq5/orig | https://avatars.mds.yandex.net/get-yastore/21012869/rfbzjh69f6cqw8bnk645qlv9f2vwwz8s/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zswsl6dwvnc6b8gfs6xnbcdxvxm22p5j/orig</x:v>
@@ -3217,7 +3280,16 @@
         <x:v>Гибкий мрамор 114×280 см — Дуб Винтаж</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Дуб Винтаж». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Дуб Винтаж» — Фактура состаренного дерева добавляет характер и уют — подходит для интерьеров в стиле лофт, кантри и современной классики. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/wtqtqnntvvsh8zrsnh7mgg4psnkmxb7b/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mb526z5xgklm9k4529xjjs8kj8rlkckk/orig | https://avatars.mds.yandex.net/get-yastore/21044143/ftcjlr95jm5nhlr6b7tq9sknh5q4nc72/orig</x:v>
@@ -3333,7 +3405,16 @@
         <x:v>Гибкий мрамор 114×280 см — Beige Concrete</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Beige Concrete». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Beige Concrete» — Тёплый бежевый бетон выглядит мягче обычного серого и легко сочетается с деревом, белой сантехникой и спокойными натуральными цветами. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/8qw2qwg2v87gsqggrf2qlbjll858zxkf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/zvcjwnpn7l4b6bvrxq9m5k7j87gv2w95/orig | https://avatars.mds.yandex.net/get-yastore/21012869/jv4xmtjhk8cq5zmkj2klxhg9dfrn6vlm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/f6fd5rqmkhs4r9qbjs8nb45rrqckvmlg/orig</x:v>
@@ -3449,7 +3530,16 @@
         <x:v>Гибкий мрамор 114×280 см — Terrazzo White</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Гибкий мрамор для стен 114×280 см, декор «Terrazzo White». Влагостойкие панели для внутренней отделки кухни, ванной, санузла и жилых помещений. Крупный формат помогает получить минимум стыков. Монтаж выполняется на сухое, чистое и прочное основание; в душевой герметизируют стыки и примыкания. В наличии в Волгограде.</x:v>
+        <x:v>Гибкий мрамор «Terrazzo White» — Светлое терраццо оживляет интерьер деликатным рисунком и помогает сделать кухню, ванную или коммерческое пространство интереснее. ✨
+Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
+Почему это удобно:
+• влагостойкая поверхность для внутренней отделки;
+• быстрый монтаж без сложного и грязного ремонта;
+• панели легко режутся и подходят для самостоятельной установки;
+• можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
+• поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
+📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/zvg5c7xvfp27vb94x8dgw6nw8hrkzgs8/orig | https://avatars.mds.yandex.net/get-yastore/20900992/qf62gg7v6c79zx5nz7bbkffmx542n4ws/orig | https://avatars.mds.yandex.net/get-yastore/20900992/j8c85d75scqcql2tbc6z56sfwncft7gd/orig</x:v>
@@ -3622,41 +3712,41 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="R6fab10e90cd74271"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="Rc1feed44285c40ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="R70503f53de9c4337"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="R1a5d872047244319"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="Ra140bb46042545e5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="R06e95f5ecb6b4d52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R0f6cbfa7808b4e78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="Rc98995f1d6ef4575"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="R271c6fae8b9842b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R34fe0d7f90b64231"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R05f9aaa93c604fa8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Ra54a112802bc4d6e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="Rf90f5902d7234420"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R235be6ec6c6f4d54"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="R77dcbaac1c7a4dc4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="Rf01854a876024275"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R106b7ffb723f4341"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R93e46dda28ff42cc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R8ef5ec54e38b41dc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R1780485268b94ea4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R5ef73f9a616c46e2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Rb7666a6c84b74a73"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R68bfb2f7d8aa42cc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R43d750be78784742"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="Rf372730f40174f82"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="Ra692a31f41734abd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="Rba554dd6214c402f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="R4f084fbd8564489e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R8da4be5825b94edb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R91f52c1e6e874932"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="R406fef69a26742d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="R248e417d2fbb41fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="R66627099b245408d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="Rf9e090176fa149c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="Re6ed6244bd254e6e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="R6829ef8300af4dd2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="R8c2fea6788374ad3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="R5f2b07a4ddd24a32"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="Rab79290f764044d4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="R179f66ab5b384688"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Ra0c25c5487e24635"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Raf21792d04394841"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R61975c9f395d4fac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="Rc34196702f804683"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R3d62a505dfb64f77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R2e2766e7d9c44980"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rce982e98f96c45b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R38c49cc6a1164473"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="Rc7f4ef6463c246c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="R8f999a4bc6064e30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="Rbb5f0a528dc5468e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R4601a630c1514713"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="Rcf9eb065beaf42be"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="Rb525cb06b64a4339"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R1de00f02c6e6448d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R3219d2c4d74e4977"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="R137de94e5cd94b59"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R3efe98c22b13498c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="Rc86cdb60e7564bcd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R8e1a0e17fd1d4e2b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R8f498df1aff74ffa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="R204a2360b5b4446f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="R4ea1c9c86ac64138"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R8c7de00a90b74455"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R7a35845cd91f42d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="R8750a914a43d47e1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="Rfba2bd5a297b4768"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="R62f8fa183cf84fb9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="Ra59ba4d02c454bed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="Rfbab1449a9114dfd"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R385f1c0706314c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="Re344d806b7654e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Rfd8881d1dc88477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R8bf356f388c64afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="Rcd9716ebcc874698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Rbf952e26c44d4d4f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Instructions" localSheetId="0">Инструкция!$1:$50</x:definedName>
@@ -1800,13 +1800,13 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R3cd69109f5814563"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R982382289f284cfc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="Rf3bd5380485342c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="Rfec412531e664a85"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R266f0e9fe1f74591"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="R67332dc538894310"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="R40ba34d2bc094c0d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R82f8925e99fe4565"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R213d3ef5571c4ab9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R41c56e6b963c4c78"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="R4dd60b90f822438c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R35bfe63870bf4a71"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="R35b4fac586004c8f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="R642ba84acb67420f"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2414,7 +2414,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K5" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/hzcnmmgxsdvr4ml8wdnjqmffft5jhjtc/orig | https://avatars.mds.yandex.net/get-yastore/21044143/r4bpdkc7m46nn5nx2brwptjdqctlhk7t/orig | https://avatars.mds.yandex.net/get-yastore/21044143/dsfdgrdk2k2q2hvk56cf8v2g2z8kw4bb/orig | https://avatars.mds.yandex.net/get-yastore/20274467/dd25xxsshglhg7tztjqg92qhnc5f9g7r/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
@@ -2459,7 +2459,7 @@
       <x:c r="AG5"/>
       <x:c r="AH5"/>
       <x:c r="AI5" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ5" t="str">
         <x:v>Стройматериалы</x:v>
@@ -2539,7 +2539,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K6" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/18919159/p7r2b4mtds77d6lzdjz6ksgbcd9kgcx9/orig | https://avatars.mds.yandex.net/get-yastore/18919159/m8dvrkghm7lh2jpg5v76928tc56xbllp/orig | https://avatars.mds.yandex.net/get-yastore/21598990/nm66rkbzrndqsp86grkbf5w6rqlfpp27/orig | https://avatars.mds.yandex.net/get-yastore/19034732/9vf677trzvspc2bpjpbhzgv6ph79w6sf/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bdz5sbrvkr2z6wxw626w5jrxx6shbvwq/orig</x:v>
@@ -2584,7 +2584,7 @@
       <x:c r="AG6"/>
       <x:c r="AH6"/>
       <x:c r="AI6" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ6" t="str">
         <x:v>Стройматериалы</x:v>
@@ -2664,7 +2664,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K7" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jxvfhrwn5qgx4v29kj74p2wknsjtqjl5/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xmsrjq5wl6dpz7gq6v98f4vcwxvc692s/orig | https://avatars.mds.yandex.net/get-yastore/20760651/x8lfdrwhmtgbsnqkbj5cb6chhvvntlwl/orig | https://avatars.mds.yandex.net/get-yastore/20760651/87jmpptxgkltrl79k95488prdfqjn2w6/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
@@ -2709,7 +2709,7 @@
       <x:c r="AG7"/>
       <x:c r="AH7"/>
       <x:c r="AI7" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ7" t="str">
         <x:v>Стройматериалы</x:v>
@@ -2789,7 +2789,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/zchqpmj7gl7k4c5lz72mxv5cr8n6mms7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4pznjgzkm2wf9qbtrbz4xfn7hg8mhm4j/orig | https://avatars.mds.yandex.net/get-yastore/20918687/7l568nzcwmdvm6jwwgd7srnfxvl8c6p8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/4qvg5mb65w8ptttxbbj8qch54784c4d5/orig</x:v>
@@ -2834,7 +2834,7 @@
       <x:c r="AG8"/>
       <x:c r="AH8"/>
       <x:c r="AI8" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ8" t="str">
         <x:v>Стройматериалы</x:v>
@@ -2914,7 +2914,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20811730/cqpzstj9nzd8wrbprll9frnrl6x9g4wp/orig | https://avatars.mds.yandex.net/get-yastore/21497181/nwc5cp78n76vn97z555g2zlbvfmf22kl/orig | https://avatars.mds.yandex.net/get-yastore/21598990/6cxjqfncddsz5hcd72mb8mc7nlplxd5h/orig | https://avatars.mds.yandex.net/get-yastore/19034732/s67p8kgt597xq9kzwvdhs9x4k4knk4b5/orig | https://avatars.mds.yandex.net/get-yastore/19034732/d95z2nt8lmf8rvq68qtgvmvdskjnj665/orig</x:v>
@@ -2959,7 +2959,7 @@
       <x:c r="AG9"/>
       <x:c r="AH9"/>
       <x:c r="AI9" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ9" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3039,7 +3039,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21580234/kqljphlmrr8v4ftp5q7fgnc7m2x6mwxg/orig | https://avatars.mds.yandex.net/get-yastore/20811730/z2jfrv44x46kw2xnqxjdmcjlkjjkc7qt/orig | https://avatars.mds.yandex.net/get-yastore/19782553/gqwpd5z6k62dbtwxtm4dptjtf2jmqpdz/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bvccxxtwvgdx2f6l9vjgxn94s2jrzrwk/orig</x:v>
@@ -3084,7 +3084,7 @@
       <x:c r="AG10"/>
       <x:c r="AH10"/>
       <x:c r="AI10" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ10" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3164,7 +3164,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/9hcv6xhdxnfjrwwd98qg92wl4v5lgz6f/orig | https://avatars.mds.yandex.net/get-yastore/20274467/jsx9k6l9fsmls57rbgv52zbzcrt5zwq5/orig | https://avatars.mds.yandex.net/get-yastore/21012869/rfbzjh69f6cqw8bnk645qlv9f2vwwz8s/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zswsl6dwvnc6b8gfs6xnbcdxvxm22p5j/orig</x:v>
@@ -3209,7 +3209,7 @@
       <x:c r="AG11"/>
       <x:c r="AH11"/>
       <x:c r="AI11" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ11" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3289,7 +3289,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/wtqtqnntvvsh8zrsnh7mgg4psnkmxb7b/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mb526z5xgklm9k4529xjjs8kj8rlkckk/orig | https://avatars.mds.yandex.net/get-yastore/21044143/ftcjlr95jm5nhlr6b7tq9sknh5q4nc72/orig</x:v>
@@ -3334,7 +3334,7 @@
       <x:c r="AG12"/>
       <x:c r="AH12"/>
       <x:c r="AI12" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ12" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3414,7 +3414,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/8qw2qwg2v87gsqggrf2qlbjll858zxkf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/zvcjwnpn7l4b6bvrxq9m5k7j87gv2w95/orig | https://avatars.mds.yandex.net/get-yastore/21012869/jv4xmtjhk8cq5zmkj2klxhg9dfrn6vlm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/f6fd5rqmkhs4r9qbjs8nb45rrqckvmlg/orig</x:v>
@@ -3459,7 +3459,7 @@
       <x:c r="AG13"/>
       <x:c r="AH13"/>
       <x:c r="AI13" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ13" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3539,7 +3539,7 @@
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Посмотреть декор можно в нашей точке в Волгограде. Напишите размеры стены — поможем сориентироваться по количеству панелей.</x:v>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/zvg5c7xvfp27vb94x8dgw6nw8hrkzgs8/orig | https://avatars.mds.yandex.net/get-yastore/20900992/qf62gg7v6c79zx5nz7bbkffmx542n4ws/orig | https://avatars.mds.yandex.net/get-yastore/20900992/j8c85d75scqcql2tbc6z56sfwncft7gd/orig</x:v>
@@ -3584,7 +3584,7 @@
       <x:c r="AG14"/>
       <x:c r="AH14"/>
       <x:c r="AI14" t="n">
-        <x:v>4900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="AJ14" t="str">
         <x:v>Стройматериалы</x:v>
@@ -3712,41 +3712,41 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="R6829ef8300af4dd2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="R8c2fea6788374ad3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="R5f2b07a4ddd24a32"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="Rab79290f764044d4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="R179f66ab5b384688"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Ra0c25c5487e24635"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Raf21792d04394841"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R61975c9f395d4fac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="Rc34196702f804683"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R3d62a505dfb64f77"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R2e2766e7d9c44980"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rce982e98f96c45b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R38c49cc6a1164473"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="Rc7f4ef6463c246c0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="R8f999a4bc6064e30"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="Rbb5f0a528dc5468e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R4601a630c1514713"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="Rcf9eb065beaf42be"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="Rb525cb06b64a4339"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R1de00f02c6e6448d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R3219d2c4d74e4977"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="R137de94e5cd94b59"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R3efe98c22b13498c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="Rc86cdb60e7564bcd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R8e1a0e17fd1d4e2b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R8f498df1aff74ffa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="R204a2360b5b4446f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="R4ea1c9c86ac64138"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R8c7de00a90b74455"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R7a35845cd91f42d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="R8750a914a43d47e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="Rfba2bd5a297b4768"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="R62f8fa183cf84fb9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="Ra59ba4d02c454bed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="Rfbab1449a9114dfd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="Rd6f4c019d8194629"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="Ra25fa2bb2c2b43d3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="R1d1baf6cb58f4827"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="R5af57958d1e54d33"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="Rf02e7e2a0e3e4761"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Ra10a4e32c51044c2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Rb65e311f57a84fd4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="Rcf5f867ac9f94543"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="Ra5508d06a1fc44ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="Rfcb0040e9f83478b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R4432fd87ea7d403b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rd762496555474cf5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R0495202bcd2d4982"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R32c27632e0af43b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="Rc99279436cd84cd5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R9bba48821dcc4177"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R429bf3ef8bbb472a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R59e5208f8f2b442a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R716490a1ca18460e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="Rb37870dfd4a2499c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="Rbf1ffb28b3d2454a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Rcb5f9eee8e0349e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="Rc4f57e4e55a74ef6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R790906c0d1114463"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R452d6531b5ba4b55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R2c51523ca153423d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="R83830b98f1c4454c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="Rc0bf41f8ab0442c7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R9b088e6d4a134a1f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R269b2ef71a1b402b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="Rdf3d2f0288314aa4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="R18f2c8846c9b4037"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="R3b24af5abf2a48ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="R1717422f8fa44410"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="R5603ea4ac4c74d85"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R8bf356f388c64afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="Rcd9716ebcc874698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Rbf952e26c44d4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R7909d87558734447"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="2" r:id="R3148eecbbb7a408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="3" r:id="Rff80789572e6473c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Instructions" localSheetId="0">Инструкция!$1:$50</x:definedName>
@@ -21,7 +21,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="16"/>
+        <x:sz val="1600"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -32,7 +33,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="16"/>
+        <x:sz val="1600"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -43,7 +45,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -53,7 +56,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -64,7 +68,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -75,7 +79,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -86,7 +91,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -98,7 +103,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -108,7 +114,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -117,7 +124,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -125,7 +133,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -139,7 +148,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -149,7 +159,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -157,7 +168,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -167,7 +179,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -175,7 +188,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -185,7 +199,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -193,7 +208,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -204,7 +220,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -214,7 +231,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -223,7 +241,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -231,7 +250,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -241,7 +261,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -250,7 +271,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -258,7 +280,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -268,7 +291,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -277,7 +301,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -285,7 +310,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -295,7 +321,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -304,7 +331,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -312,7 +340,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -322,7 +351,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -331,7 +361,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -339,7 +370,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -350,7 +382,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -360,7 +393,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -371,7 +405,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -380,7 +415,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -388,7 +424,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -401,7 +438,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -412,7 +449,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -421,7 +459,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -429,7 +468,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -441,7 +481,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -449,7 +490,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -461,7 +503,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -472,7 +514,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -481,7 +524,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -489,7 +533,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -502,7 +547,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -512,7 +558,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -523,7 +570,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -535,7 +582,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -545,7 +593,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -554,7 +603,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -562,7 +612,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -577,7 +628,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -585,7 +637,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -596,7 +649,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -606,7 +660,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -617,7 +672,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -629,7 +684,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -639,7 +695,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -650,7 +707,7 @@
     <x:r>
       <x:rPr>
         <x:u val="single"/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF1265BE"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -661,7 +718,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -672,7 +730,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="14"/>
+        <x:sz val="1400"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -682,7 +741,8 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -691,7 +751,8 @@
     <x:r>
       <x:rPr>
         <x:b/>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -699,7 +760,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1800,13 +1862,13 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R82f8925e99fe4565"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R213d3ef5571c4ab9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R41c56e6b963c4c78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="R4dd60b90f822438c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="R35bfe63870bf4a71"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="R35b4fac586004c8f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="R642ba84acb67420f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Rf7b29a9aaf7c47b1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="R9ffdf4531bf84906"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="R7da893f3fb5b4c09"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="R7ffcca03c3024d8b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="Rdd9fd7f9f0534b7b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="Rff020c1f12064677"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="Re6a42789d80544d3"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2413,6 +2475,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -2439,7 +2503,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W5" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X5" t="n">
         <x:v>1</x:v>
@@ -2538,6 +2602,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -2564,7 +2630,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W6" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X6" t="n">
         <x:v>1</x:v>
@@ -2663,6 +2729,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -2689,7 +2757,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W7" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X7" t="n">
         <x:v>1</x:v>
@@ -2788,6 +2856,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -2814,7 +2884,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W8" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X8" t="n">
         <x:v>1</x:v>
@@ -2913,6 +2983,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -2939,7 +3011,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W9" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X9" t="n">
         <x:v>1</x:v>
@@ -3038,6 +3110,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -3064,7 +3138,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W10" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X10" t="n">
         <x:v>1</x:v>
@@ -3163,6 +3237,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -3189,7 +3265,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W11" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X11" t="n">
         <x:v>1</x:v>
@@ -3288,6 +3364,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -3314,7 +3392,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W12" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X12" t="n">
         <x:v>1</x:v>
@@ -3413,6 +3491,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -3439,7 +3519,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W13" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X13" t="n">
         <x:v>1</x:v>
@@ -3538,6 +3618,8 @@
 • панели легко режутся и подходят для самостоятельной установки;
 • можно монтировать на прочную плитку, бетон, штукатурку, гипсокартон, МДФ или фанеру;
 • поставляются в скрученном виде — удобно перевозить и поднимать в квартиру.
+✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
+🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
 📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
       </x:c>
@@ -3564,7 +3646,7 @@
         <x:v>Поштучно</x:v>
       </x:c>
       <x:c r="W14" t="n">
-        <x:v>1</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="X14" t="n">
         <x:v>1</x:v>
@@ -3712,41 +3794,41 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="Rd6f4c019d8194629"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="Ra25fa2bb2c2b43d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="R1d1baf6cb58f4827"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="R5af57958d1e54d33"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="Rf02e7e2a0e3e4761"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Ra10a4e32c51044c2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="Rb65e311f57a84fd4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="Rcf5f867ac9f94543"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="Ra5508d06a1fc44ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="Rfcb0040e9f83478b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="R4432fd87ea7d403b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="Rd762496555474cf5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R0495202bcd2d4982"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R32c27632e0af43b4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="Rc99279436cd84cd5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R9bba48821dcc4177"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="R429bf3ef8bbb472a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R59e5208f8f2b442a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R716490a1ca18460e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="Rb37870dfd4a2499c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="Rbf1ffb28b3d2454a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Rcb5f9eee8e0349e3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="Rc4f57e4e55a74ef6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R790906c0d1114463"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="R452d6531b5ba4b55"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R2c51523ca153423d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="R83830b98f1c4454c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="Rc0bf41f8ab0442c7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R9b088e6d4a134a1f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R269b2ef71a1b402b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="Rdf3d2f0288314aa4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="R18f2c8846c9b4037"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="R3b24af5abf2a48ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="R1717422f8fa44410"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="R5603ea4ac4c74d85"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="Rea6b878ba1584c82"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="Rffcd1e82f37243e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="Ra3ff24d102ee483e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="Reefecc3724834ade"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="R7c16469b88294280"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Rbff4240dda3c4a29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R9c9b0308681d46f7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="Rc676019c77dc46ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="R38bc42fc5e6f411f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R9cae3f0627c94d45"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="Rb8bf83eb26ac4168"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R6cc914c6221340fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R750f17f48c3f4c26"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R5d987a6201aa48b7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="R11a06d40f3f5477a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R70ef320968794330"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="Reb3d61cec0664f06"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R63a9b7d0ee9d41e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R1e263f6e6b0b4c37"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R3cd3ee5789ab4816"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R15808d00529649a2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Rf3f871d95b374969"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R32a1709f23334630"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R8c81295c80754b05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="Rb1634ce95d0d4720"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R56aa562a92bd4d00"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="Ra68f4de53b444d91"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="Rf466549f79334c5a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R05bcd72c4a254595"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R77271d982ff54b0a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="Rfdd6dc72e7494f81"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="Re42e2875f7574ec0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="Rd3442b770b2144b9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="Rfd45c17df47d49ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="R1a8e4adffa5f48b5"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -1875,599 +1875,599 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:cols>
-    <x:col min="1" max="1" width="28.329999923706055" customWidth="1"/>
-    <x:col min="2" max="2" width="17" customWidth="1"/>
-    <x:col min="3" max="3" width="20" customWidth="1"/>
-    <x:col min="4" max="4" width="17" customWidth="1"/>
-    <x:col min="5" max="5" width="18" customWidth="1"/>
-    <x:col min="6" max="6" width="25" customWidth="1"/>
-    <x:col min="7" max="8" width="16" customWidth="1"/>
-    <x:col min="9" max="10" width="19" customWidth="1"/>
-    <x:col min="11" max="13" width="16" customWidth="1"/>
-    <x:col min="14" max="16" width="28.329999923706055" customWidth="1"/>
-    <x:col min="17" max="20" width="16" customWidth="1"/>
-    <x:col min="21" max="21" width="20" customWidth="1"/>
-    <x:col min="22" max="23" width="16" customWidth="1"/>
-    <x:col min="24" max="24" width="17" customWidth="1"/>
-    <x:col min="25" max="25" width="28.329999923706055" customWidth="1"/>
-    <x:col min="26" max="27" width="16" customWidth="1"/>
-    <x:col min="28" max="28" width="28.329999923706055" customWidth="1"/>
-    <x:col min="29" max="29" width="16" customWidth="1"/>
-    <x:col min="30" max="30" width="18" customWidth="1"/>
-    <x:col min="31" max="31" width="20" customWidth="1"/>
-    <x:col min="32" max="33" width="21" customWidth="1"/>
-    <x:col min="34" max="41" width="16" customWidth="1"/>
-    <x:col min="42" max="42" width="25" customWidth="1"/>
-    <x:col min="43" max="43" width="28.329999923706055" customWidth="1"/>
-    <x:col min="44" max="44" width="16" customWidth="1"/>
-    <x:col min="45" max="46" width="18" customWidth="1"/>
-    <x:col min="47" max="50" width="16" customWidth="1"/>
-    <x:col min="51" max="51" width="23" customWidth="1"/>
-    <x:col min="52" max="52" width="28.329999923706055" customWidth="1"/>
-    <x:col min="53" max="53" width="16" customWidth="1"/>
-    <x:col min="54" max="54" width="20" customWidth="1"/>
-    <x:col min="55" max="55" width="23" customWidth="1"/>
-    <x:col min="56" max="56" width="16" customWidth="1"/>
-    <x:col min="57" max="57" width="20" customWidth="1"/>
-    <x:col min="58" max="59" width="28.329999923706055" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="50" customHeight="1">
-      <x:c r="A1" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" s="6" customFormat="1">
-      <x:c r="A2" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F2" s="7" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G2" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H2" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I2" s="7" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L2" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M2" s="7" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N2" s="7" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O2" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P2" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="Q2" s="7" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="R2" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="S2" s="7" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="T2" s="7" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="U2" s="7" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="V2" s="7" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="W2" s="7" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X2" s="7" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="Y2" s="7" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="Z2" s="7" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="AA2" s="7" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="AB2" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AC2" s="7" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AD2" s="7" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="AE2" s="7" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="AF2" s="7" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="AG2" s="7" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="AH2" s="7" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="AI2" s="7" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="AJ2" s="7" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="AK2" s="7" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="AL2" s="7" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="AM2" s="7" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="AN2" s="7" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="AO2" s="7" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="AP2" s="7" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AQ2" s="7" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="AR2" s="7" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="AS2" s="7" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="AT2" s="7" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AU2" s="7" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AV2" s="7" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AW2" s="7" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="AX2" s="7" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="AY2" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AZ2" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="BA2" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="BB2" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="BC2" s="7" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="BD2" s="7" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="BE2" s="7" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="BF2" s="7" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="BG2" s="7"/>
-    </x:row>
-    <x:row r="3" s="6" customFormat="1" ht="45" customHeight="1">
-      <x:c r="A3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="K3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="L3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="M3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="N3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="O3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="P3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="Q3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="R3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="S3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="T3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="U3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="V3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="W3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="X3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="Y3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="Z3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AA3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AB3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AC3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AD3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AE3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AF3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AG3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AH3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AI3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AJ3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AK3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AL3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AM3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AN3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AO3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AP3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AQ3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AR3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AS3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AT3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AU3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AV3" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="AW3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AX3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="AY3" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="AZ3" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BA3" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BB3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BC3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BD3" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BE3" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BF3" s="6" t="s">
-        <x:v>97</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="I4" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="J4" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="L4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="M4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="N4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="O4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="P4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="Q4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="R4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="S4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="T4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="U4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="V4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="W4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="X4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="Y4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="Z4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AA4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AB4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AC4" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="AD4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AE4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AF4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AG4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AH4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AI4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AJ4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AK4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AL4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AM4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AN4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AO4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AP4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AQ4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AR4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AS4" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="AT4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AU4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AV4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="AW4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AX4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AY4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AZ4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="BA4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="BB4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="BC4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="BD4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="BE4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="BF4" s="5" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>adamar-vlg-WHITE CONCRETE_1</x:v>
-      </x:c>
-      <x:c r="B5"/>
-      <x:c r="C5"/>
-      <x:c r="D5"/>
-      <x:c r="E5"/>
-      <x:c r="F5"/>
-      <x:c r="G5" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>Гибкий мрамор 114×280 см — WHITE CONCRETE</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>Гибкий мрамор «WHITE CONCRETE» — Светлый бетонный рисунок выглядит современно и не перегружает интерьер — хороший фон для минимализма, лофта и спокойных светлых пространств. ✨
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="2" max="2" width="17" customWidth="1"/>
+    <ns0:col min="3" max="3" width="20" customWidth="1"/>
+    <ns0:col min="4" max="4" width="17" customWidth="1"/>
+    <ns0:col min="5" max="5" width="18" customWidth="1"/>
+    <ns0:col min="6" max="6" width="25" customWidth="1"/>
+    <ns0:col min="7" max="8" width="16" customWidth="1"/>
+    <ns0:col min="9" max="10" width="19" customWidth="1"/>
+    <ns0:col min="11" max="13" width="16" customWidth="1"/>
+    <ns0:col min="14" max="16" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="17" max="20" width="16" customWidth="1"/>
+    <ns0:col min="21" max="21" width="20" customWidth="1"/>
+    <ns0:col min="22" max="23" width="16" customWidth="1"/>
+    <ns0:col min="24" max="24" width="17" customWidth="1"/>
+    <ns0:col min="25" max="25" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="26" max="27" width="16" customWidth="1"/>
+    <ns0:col min="28" max="28" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="29" max="29" width="16" customWidth="1"/>
+    <ns0:col min="30" max="30" width="18" customWidth="1"/>
+    <ns0:col min="31" max="31" width="20" customWidth="1"/>
+    <ns0:col min="32" max="33" width="21" customWidth="1"/>
+    <ns0:col min="34" max="41" width="16" customWidth="1"/>
+    <ns0:col min="42" max="42" width="25" customWidth="1"/>
+    <ns0:col min="43" max="43" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="44" max="44" width="16" customWidth="1"/>
+    <ns0:col min="45" max="46" width="18" customWidth="1"/>
+    <ns0:col min="47" max="50" width="16" customWidth="1"/>
+    <ns0:col min="51" max="51" width="23" customWidth="1"/>
+    <ns0:col min="52" max="52" width="28.329999923706055" customWidth="1"/>
+    <ns0:col min="53" max="53" width="16" customWidth="1"/>
+    <ns0:col min="54" max="54" width="20" customWidth="1"/>
+    <ns0:col min="55" max="55" width="23" customWidth="1"/>
+    <ns0:col min="56" max="56" width="16" customWidth="1"/>
+    <ns0:col min="57" max="57" width="20" customWidth="1"/>
+    <ns0:col min="58" max="59" width="28.329999923706055" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="50" customHeight="1">
+      <ns0:c r="A1" s="4" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" s="6" customFormat="1">
+      <ns0:c r="A2" s="7" t="s">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="7" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="7" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="7" t="s">
+        <ns0:v>41</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="7" t="s">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="7" t="s">
+        <ns0:v>43</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="7" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="7" t="s">
+        <ns0:v>45</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="7" t="s">
+        <ns0:v>46</ns0:v>
+      </ns0:c>
+      <ns0:c r="J2" s="7" t="s">
+        <ns0:v>47</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" s="7" t="s">
+        <ns0:v>48</ns0:v>
+      </ns0:c>
+      <ns0:c r="L2" s="7" t="s">
+        <ns0:v>49</ns0:v>
+      </ns0:c>
+      <ns0:c r="M2" s="7" t="s">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="N2" s="7" t="s">
+        <ns0:v>51</ns0:v>
+      </ns0:c>
+      <ns0:c r="O2" s="7" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="P2" s="7" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q2" s="7" t="s">
+        <ns0:v>54</ns0:v>
+      </ns0:c>
+      <ns0:c r="R2" s="7" t="s">
+        <ns0:v>55</ns0:v>
+      </ns0:c>
+      <ns0:c r="S2" s="7" t="s">
+        <ns0:v>56</ns0:v>
+      </ns0:c>
+      <ns0:c r="T2" s="7" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="U2" s="7" t="s">
+        <ns0:v>58</ns0:v>
+      </ns0:c>
+      <ns0:c r="V2" s="7" t="s">
+        <ns0:v>59</ns0:v>
+      </ns0:c>
+      <ns0:c r="W2" s="7" t="s">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="X2" s="7" t="s">
+        <ns0:v>61</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y2" s="7" t="s">
+        <ns0:v>62</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z2" s="7" t="s">
+        <ns0:v>63</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA2" s="7" t="s">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB2" s="7" t="s">
+        <ns0:v>65</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC2" s="7" t="s">
+        <ns0:v>66</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD2" s="7" t="s">
+        <ns0:v>67</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE2" s="7" t="s">
+        <ns0:v>68</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF2" s="7" t="s">
+        <ns0:v>69</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG2" s="7" t="s">
+        <ns0:v>70</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH2" s="7" t="s">
+        <ns0:v>71</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI2" s="7" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ2" s="7" t="s">
+        <ns0:v>73</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK2" s="7" t="s">
+        <ns0:v>74</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL2" s="7" t="s">
+        <ns0:v>75</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM2" s="7" t="s">
+        <ns0:v>76</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN2" s="7" t="s">
+        <ns0:v>77</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO2" s="7" t="s">
+        <ns0:v>78</ns0:v>
+      </ns0:c>
+      <ns0:c r="AP2" s="7" t="s">
+        <ns0:v>79</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ2" s="7" t="s">
+        <ns0:v>80</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR2" s="7" t="s">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS2" s="7" t="s">
+        <ns0:v>82</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT2" s="7" t="s">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU2" s="7" t="s">
+        <ns0:v>84</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV2" s="7" t="s">
+        <ns0:v>85</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW2" s="7" t="s">
+        <ns0:v>86</ns0:v>
+      </ns0:c>
+      <ns0:c r="AX2" s="7" t="s">
+        <ns0:v>87</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY2" s="7" t="s">
+        <ns0:v>88</ns0:v>
+      </ns0:c>
+      <ns0:c r="AZ2" s="7" t="s">
+        <ns0:v>89</ns0:v>
+      </ns0:c>
+      <ns0:c r="BA2" s="7" t="s">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="BB2" s="7" t="s">
+        <ns0:v>91</ns0:v>
+      </ns0:c>
+      <ns0:c r="BC2" s="7" t="s">
+        <ns0:v>92</ns0:v>
+      </ns0:c>
+      <ns0:c r="BD2" s="7" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="BE2" s="7" t="s">
+        <ns0:v>94</ns0:v>
+      </ns0:c>
+      <ns0:c r="BF2" s="7" t="s">
+        <ns0:v>95</ns0:v>
+      </ns0:c>
+      <ns0:c r="BG2" s="7"/>
+    </ns0:row>
+    <ns0:row r="3" s="6" customFormat="1" ht="45" customHeight="1">
+      <ns0:c r="A3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="M3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="N3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="O3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="P3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="R3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="S3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="T3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="U3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="V3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="W3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="X3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AP3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV3" s="6" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AX3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY3" s="6" t="s">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="AZ3" s="6" t="s">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="BA3" s="6" t="s">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="BB3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="BC3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="BD3" s="6" t="s">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="BE3" s="6" t="s">
+        <ns0:v>98</ns0:v>
+      </ns0:c>
+      <ns0:c r="BF3" s="6" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="B4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="I4" t="s">
+        <ns0:v>101</ns0:v>
+      </ns0:c>
+      <ns0:c r="J4" t="s">
+        <ns0:v>101</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="L4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="M4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="N4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="O4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="P4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="R4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="S4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="T4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="U4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="V4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="W4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="X4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AB4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AC4" t="s">
+        <ns0:v>102</ns0:v>
+      </ns0:c>
+      <ns0:c r="AD4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AE4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AF4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AG4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AH4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AI4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AP4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS4" t="s">
+        <ns0:v>102</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AX4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="AZ4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="BA4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="BB4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="BC4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="BD4" t="s">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="BE4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+      <ns0:c r="BF4" s="5" t="s">
+        <ns0:v>99</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" t="str">
+        <ns0:v>adamar-vlg-WHITE CONCRETE_1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5"/>
+      <ns0:c r="C5"/>
+      <ns0:c r="D5"/>
+      <ns0:c r="E5"/>
+      <ns0:c r="F5"/>
+      <ns0:c r="G5" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I5" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — WHITE CONCRETE</ns0:v>
+      </ns0:c>
+      <ns0:c r="J5" t="str">
+        <ns0:v>Гибкий мрамор «WHITE CONCRETE» — Светлый бетонный рисунок выглядит современно и не перегружает интерьер — хороший фон для минимализма, лофта и спокойных светлых пространств. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -2478,123 +2478,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/hzcnmmgxsdvr4ml8wdnjqmffft5jhjtc/orig | https://avatars.mds.yandex.net/get-yastore/21044143/r4bpdkc7m46nn5nx2brwptjdqctlhk7t/orig | https://avatars.mds.yandex.net/get-yastore/21044143/dsfdgrdk2k2q2hvk56cf8v2g2z8kw4bb/orig | https://avatars.mds.yandex.net/get-yastore/20274467/dd25xxsshglhg7tztjqg92qhnc5f9g7r/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
-      </x:c>
-      <x:c r="L5"/>
-      <x:c r="M5" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N5"/>
-      <x:c r="O5"/>
-      <x:c r="P5"/>
-      <x:c r="Q5" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R5" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S5"/>
-      <x:c r="T5"/>
-      <x:c r="U5"/>
-      <x:c r="V5" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W5" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z5" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA5"/>
-      <x:c r="AB5"/>
-      <x:c r="AC5"/>
-      <x:c r="AD5"/>
-      <x:c r="AE5"/>
-      <x:c r="AF5"/>
-      <x:c r="AG5"/>
-      <x:c r="AH5"/>
-      <x:c r="AI5" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ5" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK5" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL5" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM5" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN5" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO5"/>
-      <x:c r="AP5" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ5" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR5" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS5" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT5" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU5" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV5" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW5"/>
-      <x:c r="AX5" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY5"/>
-      <x:c r="AZ5"/>
-      <x:c r="BA5"/>
-      <x:c r="BB5"/>
-      <x:c r="BC5"/>
-      <x:c r="BD5"/>
-      <x:c r="BE5"/>
-      <x:c r="BF5"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>adamar-vlg-ДУБ СОНОМА</x:v>
-      </x:c>
-      <x:c r="B6"/>
-      <x:c r="C6"/>
-      <x:c r="D6"/>
-      <x:c r="E6"/>
-      <x:c r="F6"/>
-      <x:c r="G6" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H6" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I6" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Дуб Сонома</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>Гибкий мрамор «Дуб Сонома» — Тёплая древесная фактура добавляет интерьеру уюта и хорошо сочетается со светлой мебелью, спокойными стенами и натуральными оттенками. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/20760651/hzcnmmgxsdvr4ml8wdnjqmffft5jhjtc/orig | https://avatars.mds.yandex.net/get-yastore/21044143/r4bpdkc7m46nn5nx2brwptjdqctlhk7t/orig | https://avatars.mds.yandex.net/get-yastore/21044143/dsfdgrdk2k2q2hvk56cf8v2g2z8kw4bb/orig | https://avatars.mds.yandex.net/get-yastore/20274467/dd25xxsshglhg7tztjqg92qhnc5f9g7r/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L5"/>
+      <ns0:c r="M5" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N5"/>
+      <ns0:c r="O5"/>
+      <ns0:c r="P5"/>
+      <ns0:c r="Q5" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R5" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S5"/>
+      <ns0:c r="T5"/>
+      <ns0:c r="U5"/>
+      <ns0:c r="V5" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W5" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X5" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y5" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z5" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA5"/>
+      <ns0:c r="AB5"/>
+      <ns0:c r="AC5"/>
+      <ns0:c r="AD5"/>
+      <ns0:c r="AE5"/>
+      <ns0:c r="AF5"/>
+      <ns0:c r="AG5"/>
+      <ns0:c r="AH5"/>
+      <ns0:c r="AI5" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ5" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK5" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL5" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM5" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN5" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO5"/>
+      <ns0:c r="AP5" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ5" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR5" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS5" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT5" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU5" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV5" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW5"/>
+      <ns0:c r="AX5" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY5"/>
+      <ns0:c r="AZ5"/>
+      <ns0:c r="BA5"/>
+      <ns0:c r="BB5"/>
+      <ns0:c r="BC5"/>
+      <ns0:c r="BD5"/>
+      <ns0:c r="BE5"/>
+      <ns0:c r="BF5"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" t="str">
+        <ns0:v>adamar-vlg-ДУБ СОНОМА</ns0:v>
+      </ns0:c>
+      <ns0:c r="B6"/>
+      <ns0:c r="C6"/>
+      <ns0:c r="D6"/>
+      <ns0:c r="E6"/>
+      <ns0:c r="F6"/>
+      <ns0:c r="G6" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I6" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Дуб Сонома</ns0:v>
+      </ns0:c>
+      <ns0:c r="J6" t="str">
+        <ns0:v>Гибкий мрамор «Дуб Сонома» — Тёплая древесная фактура добавляет интерьеру уюта и хорошо сочетается со светлой мебелью, спокойными стенами и натуральными оттенками. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -2605,123 +2605,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/18919159/p7r2b4mtds77d6lzdjz6ksgbcd9kgcx9/orig | https://avatars.mds.yandex.net/get-yastore/18919159/m8dvrkghm7lh2jpg5v76928tc56xbllp/orig | https://avatars.mds.yandex.net/get-yastore/21598990/nm66rkbzrndqsp86grkbf5w6rqlfpp27/orig | https://avatars.mds.yandex.net/get-yastore/19034732/9vf677trzvspc2bpjpbhzgv6ph79w6sf/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bdz5sbrvkr2z6wxw626w5jrxx6shbvwq/orig</x:v>
-      </x:c>
-      <x:c r="L6"/>
-      <x:c r="M6" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N6"/>
-      <x:c r="O6"/>
-      <x:c r="P6"/>
-      <x:c r="Q6" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R6" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S6"/>
-      <x:c r="T6"/>
-      <x:c r="U6"/>
-      <x:c r="V6" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W6" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z6" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA6"/>
-      <x:c r="AB6"/>
-      <x:c r="AC6"/>
-      <x:c r="AD6"/>
-      <x:c r="AE6"/>
-      <x:c r="AF6"/>
-      <x:c r="AG6"/>
-      <x:c r="AH6"/>
-      <x:c r="AI6" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ6" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK6" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL6" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM6" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN6" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO6"/>
-      <x:c r="AP6" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ6" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR6" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS6" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT6" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU6" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV6" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW6"/>
-      <x:c r="AX6" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY6"/>
-      <x:c r="AZ6"/>
-      <x:c r="BA6"/>
-      <x:c r="BB6"/>
-      <x:c r="BC6"/>
-      <x:c r="BD6"/>
-      <x:c r="BE6"/>
-      <x:c r="BF6"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>adamar-vlg-WHITE CONCRETE FON</x:v>
-      </x:c>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>Гибкий мрамор 114×280 см — White Concrete Fon</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>Гибкий мрамор «White Concrete Fon» — Мягкий светлый бетон создаёт аккуратный нейтральный фон и визуально делает пространство легче — особенно удачно смотрится в кухне и ванной. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/18919159/p7r2b4mtds77d6lzdjz6ksgbcd9kgcx9/orig | https://avatars.mds.yandex.net/get-yastore/18919159/m8dvrkghm7lh2jpg5v76928tc56xbllp/orig | https://avatars.mds.yandex.net/get-yastore/21598990/nm66rkbzrndqsp86grkbf5w6rqlfpp27/orig | https://avatars.mds.yandex.net/get-yastore/19034732/9vf677trzvspc2bpjpbhzgv6ph79w6sf/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bdz5sbrvkr2z6wxw626w5jrxx6shbvwq/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L6"/>
+      <ns0:c r="M6" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N6"/>
+      <ns0:c r="O6"/>
+      <ns0:c r="P6"/>
+      <ns0:c r="Q6" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R6" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S6"/>
+      <ns0:c r="T6"/>
+      <ns0:c r="U6"/>
+      <ns0:c r="V6" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W6" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X6" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y6" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z6" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA6"/>
+      <ns0:c r="AB6"/>
+      <ns0:c r="AC6"/>
+      <ns0:c r="AD6"/>
+      <ns0:c r="AE6"/>
+      <ns0:c r="AF6"/>
+      <ns0:c r="AG6"/>
+      <ns0:c r="AH6"/>
+      <ns0:c r="AI6" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ6" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK6" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL6" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM6" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN6" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO6"/>
+      <ns0:c r="AP6" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ6" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR6" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS6" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT6" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU6" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV6" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW6"/>
+      <ns0:c r="AX6" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY6"/>
+      <ns0:c r="AZ6"/>
+      <ns0:c r="BA6"/>
+      <ns0:c r="BB6"/>
+      <ns0:c r="BC6"/>
+      <ns0:c r="BD6"/>
+      <ns0:c r="BE6"/>
+      <ns0:c r="BF6"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" t="str">
+        <ns0:v>adamar-vlg-WHITE CONCRETE FON</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7"/>
+      <ns0:c r="C7"/>
+      <ns0:c r="D7"/>
+      <ns0:c r="E7"/>
+      <ns0:c r="F7"/>
+      <ns0:c r="G7" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — White Concrete Fon</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7" t="str">
+        <ns0:v>Гибкий мрамор «White Concrete Fon» — Мягкий светлый бетон создаёт аккуратный нейтральный фон и визуально делает пространство легче — особенно удачно смотрится в кухне и ванной. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -2732,123 +2732,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/jxvfhrwn5qgx4v29kj74p2wknsjtqjl5/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xmsrjq5wl6dpz7gq6v98f4vcwxvc692s/orig | https://avatars.mds.yandex.net/get-yastore/20760651/x8lfdrwhmtgbsnqkbj5cb6chhvvntlwl/orig | https://avatars.mds.yandex.net/get-yastore/20760651/87jmpptxgkltrl79k95488prdfqjn2w6/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</x:v>
-      </x:c>
-      <x:c r="L7"/>
-      <x:c r="M7" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N7"/>
-      <x:c r="O7"/>
-      <x:c r="P7"/>
-      <x:c r="Q7" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R7" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S7"/>
-      <x:c r="T7"/>
-      <x:c r="U7"/>
-      <x:c r="V7" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W7" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z7" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA7"/>
-      <x:c r="AB7"/>
-      <x:c r="AC7"/>
-      <x:c r="AD7"/>
-      <x:c r="AE7"/>
-      <x:c r="AF7"/>
-      <x:c r="AG7"/>
-      <x:c r="AH7"/>
-      <x:c r="AI7" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ7" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK7" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL7" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM7" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN7" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO7"/>
-      <x:c r="AP7" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ7" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR7" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS7" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT7" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU7" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV7" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW7"/>
-      <x:c r="AX7" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY7"/>
-      <x:c r="AZ7"/>
-      <x:c r="BA7"/>
-      <x:c r="BB7"/>
-      <x:c r="BC7"/>
-      <x:c r="BD7"/>
-      <x:c r="BE7"/>
-      <x:c r="BF7"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>adamar-vlg-GREY LORD_1</x:v>
-      </x:c>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H8" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I8" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Grey Lord</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>Гибкий мрамор «Grey Lord» — Выразительный серый камень помогает собрать строгий современный интерьер и подходит для акцентной стены без лишней пестроты. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/20760651/jxvfhrwn5qgx4v29kj74p2wknsjtqjl5/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xmsrjq5wl6dpz7gq6v98f4vcwxvc692s/orig | https://avatars.mds.yandex.net/get-yastore/20760651/x8lfdrwhmtgbsnqkbj5cb6chhvvntlwl/orig | https://avatars.mds.yandex.net/get-yastore/20760651/87jmpptxgkltrl79k95488prdfqjn2w6/orig | https://avatars.mds.yandex.net/get-yastore/20760651/xcw6762ckjtd79pkgxkcnc4mhlgk66f2/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L7"/>
+      <ns0:c r="M7" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N7"/>
+      <ns0:c r="O7"/>
+      <ns0:c r="P7"/>
+      <ns0:c r="Q7" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R7" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S7"/>
+      <ns0:c r="T7"/>
+      <ns0:c r="U7"/>
+      <ns0:c r="V7" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W7">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X7" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y7" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z7" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA7"/>
+      <ns0:c r="AB7"/>
+      <ns0:c r="AC7"/>
+      <ns0:c r="AD7"/>
+      <ns0:c r="AE7"/>
+      <ns0:c r="AF7"/>
+      <ns0:c r="AG7"/>
+      <ns0:c r="AH7"/>
+      <ns0:c r="AI7" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ7" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK7" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL7" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM7" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN7" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO7"/>
+      <ns0:c r="AP7" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ7" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR7" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS7" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT7" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU7" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV7" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW7"/>
+      <ns0:c r="AX7" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY7"/>
+      <ns0:c r="AZ7"/>
+      <ns0:c r="BA7"/>
+      <ns0:c r="BB7"/>
+      <ns0:c r="BC7"/>
+      <ns0:c r="BD7"/>
+      <ns0:c r="BE7"/>
+      <ns0:c r="BF7"/>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" t="str">
+        <ns0:v>adamar-vlg-GREY LORD_1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B8"/>
+      <ns0:c r="C8"/>
+      <ns0:c r="D8"/>
+      <ns0:c r="E8"/>
+      <ns0:c r="F8"/>
+      <ns0:c r="G8" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I8" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Grey Lord</ns0:v>
+      </ns0:c>
+      <ns0:c r="J8" t="str">
+        <ns0:v>Гибкий мрамор «Grey Lord» — Выразительный серый камень помогает собрать строгий современный интерьер и подходит для акцентной стены без лишней пестроты. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -2859,123 +2859,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/zchqpmj7gl7k4c5lz72mxv5cr8n6mms7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4pznjgzkm2wf9qbtrbz4xfn7hg8mhm4j/orig | https://avatars.mds.yandex.net/get-yastore/20918687/7l568nzcwmdvm6jwwgd7srnfxvl8c6p8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/4qvg5mb65w8ptttxbbj8qch54784c4d5/orig</x:v>
-      </x:c>
-      <x:c r="L8"/>
-      <x:c r="M8" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N8"/>
-      <x:c r="O8"/>
-      <x:c r="P8"/>
-      <x:c r="Q8" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R8" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S8"/>
-      <x:c r="T8"/>
-      <x:c r="U8"/>
-      <x:c r="V8" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W8" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z8" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA8"/>
-      <x:c r="AB8"/>
-      <x:c r="AC8"/>
-      <x:c r="AD8"/>
-      <x:c r="AE8"/>
-      <x:c r="AF8"/>
-      <x:c r="AG8"/>
-      <x:c r="AH8"/>
-      <x:c r="AI8" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ8" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK8" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL8" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM8" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN8" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO8"/>
-      <x:c r="AP8" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ8" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR8" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS8" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT8" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU8" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV8" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW8"/>
-      <x:c r="AX8" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY8"/>
-      <x:c r="AZ8"/>
-      <x:c r="BA8"/>
-      <x:c r="BB8"/>
-      <x:c r="BC8"/>
-      <x:c r="BD8"/>
-      <x:c r="BE8"/>
-      <x:c r="BF8"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>adamar-vlg-WHITE ROCK</x:v>
-      </x:c>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>Гибкий мрамор 114×280 см — White Rock</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>Гибкий мрамор «White Rock» — Светлая каменная текстура освежает помещение и даёт эффект цельной дорогой отделки, сохраняя спокойную цветовую гамму. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K8" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/21044143/zchqpmj7gl7k4c5lz72mxv5cr8n6mms7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/4pznjgzkm2wf9qbtrbz4xfn7hg8mhm4j/orig | https://avatars.mds.yandex.net/get-yastore/20918687/7l568nzcwmdvm6jwwgd7srnfxvl8c6p8/orig | https://avatars.mds.yandex.net/get-yastore/20274467/4qvg5mb65w8ptttxbbj8qch54784c4d5/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L8"/>
+      <ns0:c r="M8" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N8"/>
+      <ns0:c r="O8"/>
+      <ns0:c r="P8"/>
+      <ns0:c r="Q8" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R8" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S8"/>
+      <ns0:c r="T8"/>
+      <ns0:c r="U8"/>
+      <ns0:c r="V8" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W8" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X8" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y8" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z8" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA8"/>
+      <ns0:c r="AB8"/>
+      <ns0:c r="AC8"/>
+      <ns0:c r="AD8"/>
+      <ns0:c r="AE8"/>
+      <ns0:c r="AF8"/>
+      <ns0:c r="AG8"/>
+      <ns0:c r="AH8"/>
+      <ns0:c r="AI8" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ8" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK8" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL8" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM8" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN8" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO8"/>
+      <ns0:c r="AP8" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ8" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR8" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS8" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT8" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU8" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV8" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW8"/>
+      <ns0:c r="AX8" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY8"/>
+      <ns0:c r="AZ8"/>
+      <ns0:c r="BA8"/>
+      <ns0:c r="BB8"/>
+      <ns0:c r="BC8"/>
+      <ns0:c r="BD8"/>
+      <ns0:c r="BE8"/>
+      <ns0:c r="BF8"/>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" t="str">
+        <ns0:v>adamar-vlg-WHITE ROCK</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9"/>
+      <ns0:c r="C9"/>
+      <ns0:c r="D9"/>
+      <ns0:c r="E9"/>
+      <ns0:c r="F9"/>
+      <ns0:c r="G9" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I9" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — White Rock</ns0:v>
+      </ns0:c>
+      <ns0:c r="J9" t="str">
+        <ns0:v>Гибкий мрамор «White Rock» — Светлая каменная текстура освежает помещение и даёт эффект цельной дорогой отделки, сохраняя спокойную цветовую гамму. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -2986,123 +2986,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/20811730/cqpzstj9nzd8wrbprll9frnrl6x9g4wp/orig | https://avatars.mds.yandex.net/get-yastore/21497181/nwc5cp78n76vn97z555g2zlbvfmf22kl/orig | https://avatars.mds.yandex.net/get-yastore/21598990/6cxjqfncddsz5hcd72mb8mc7nlplxd5h/orig | https://avatars.mds.yandex.net/get-yastore/19034732/s67p8kgt597xq9kzwvdhs9x4k4knk4b5/orig | https://avatars.mds.yandex.net/get-yastore/19034732/d95z2nt8lmf8rvq68qtgvmvdskjnj665/orig</x:v>
-      </x:c>
-      <x:c r="L9"/>
-      <x:c r="M9" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N9"/>
-      <x:c r="O9"/>
-      <x:c r="P9"/>
-      <x:c r="Q9" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R9" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S9"/>
-      <x:c r="T9"/>
-      <x:c r="U9"/>
-      <x:c r="V9" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W9" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z9" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA9"/>
-      <x:c r="AB9"/>
-      <x:c r="AC9"/>
-      <x:c r="AD9"/>
-      <x:c r="AE9"/>
-      <x:c r="AF9"/>
-      <x:c r="AG9"/>
-      <x:c r="AH9"/>
-      <x:c r="AI9" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ9" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK9" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL9" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM9" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN9" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO9"/>
-      <x:c r="AP9" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ9" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR9" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS9" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT9" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU9" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV9" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW9"/>
-      <x:c r="AX9" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY9"/>
-      <x:c r="AZ9"/>
-      <x:c r="BA9"/>
-      <x:c r="BB9"/>
-      <x:c r="BC9"/>
-      <x:c r="BD9"/>
-      <x:c r="BE9"/>
-      <x:c r="BF9"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>adamar-vlg-ОРЕХ ТЕМНЫЙ</x:v>
-      </x:c>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I10" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Орех тёмный</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>Гибкий мрамор «Орех тёмный» — Глубокий древесный оттенок делает интерьер теплее и солиднее — красивое решение для кабинета, спальни, прихожей или акцентной стены. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/20811730/cqpzstj9nzd8wrbprll9frnrl6x9g4wp/orig | https://avatars.mds.yandex.net/get-yastore/21497181/nwc5cp78n76vn97z555g2zlbvfmf22kl/orig | https://avatars.mds.yandex.net/get-yastore/21598990/6cxjqfncddsz5hcd72mb8mc7nlplxd5h/orig | https://avatars.mds.yandex.net/get-yastore/19034732/s67p8kgt597xq9kzwvdhs9x4k4knk4b5/orig | https://avatars.mds.yandex.net/get-yastore/19034732/d95z2nt8lmf8rvq68qtgvmvdskjnj665/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L9"/>
+      <ns0:c r="M9" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N9"/>
+      <ns0:c r="O9"/>
+      <ns0:c r="P9"/>
+      <ns0:c r="Q9" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R9" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S9"/>
+      <ns0:c r="T9"/>
+      <ns0:c r="U9"/>
+      <ns0:c r="V9" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W9" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X9" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y9" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z9" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA9"/>
+      <ns0:c r="AB9"/>
+      <ns0:c r="AC9"/>
+      <ns0:c r="AD9"/>
+      <ns0:c r="AE9"/>
+      <ns0:c r="AF9"/>
+      <ns0:c r="AG9"/>
+      <ns0:c r="AH9"/>
+      <ns0:c r="AI9" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ9" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK9" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL9" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM9" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN9" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO9"/>
+      <ns0:c r="AP9" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ9" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR9" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS9" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT9" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU9" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV9" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW9"/>
+      <ns0:c r="AX9" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY9"/>
+      <ns0:c r="AZ9"/>
+      <ns0:c r="BA9"/>
+      <ns0:c r="BB9"/>
+      <ns0:c r="BC9"/>
+      <ns0:c r="BD9"/>
+      <ns0:c r="BE9"/>
+      <ns0:c r="BF9"/>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" t="str">
+        <ns0:v>adamar-vlg-ОРЕХ ТЕМНЫЙ</ns0:v>
+      </ns0:c>
+      <ns0:c r="B10"/>
+      <ns0:c r="C10"/>
+      <ns0:c r="D10"/>
+      <ns0:c r="E10"/>
+      <ns0:c r="F10"/>
+      <ns0:c r="G10" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H10" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I10" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Орех тёмный</ns0:v>
+      </ns0:c>
+      <ns0:c r="J10" t="str">
+        <ns0:v>Гибкий мрамор «Орех тёмный» — Глубокий древесный оттенок делает интерьер теплее и солиднее — красивое решение для кабинета, спальни, прихожей или акцентной стены. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -3113,123 +3113,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/21580234/kqljphlmrr8v4ftp5q7fgnc7m2x6mwxg/orig | https://avatars.mds.yandex.net/get-yastore/20811730/z2jfrv44x46kw2xnqxjdmcjlkjjkc7qt/orig | https://avatars.mds.yandex.net/get-yastore/19782553/gqwpd5z6k62dbtwxtm4dptjtf2jmqpdz/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bvccxxtwvgdx2f6l9vjgxn94s2jrzrwk/orig</x:v>
-      </x:c>
-      <x:c r="L10"/>
-      <x:c r="M10" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N10"/>
-      <x:c r="O10"/>
-      <x:c r="P10"/>
-      <x:c r="Q10" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R10" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S10"/>
-      <x:c r="T10"/>
-      <x:c r="U10"/>
-      <x:c r="V10" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W10" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z10" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA10"/>
-      <x:c r="AB10"/>
-      <x:c r="AC10"/>
-      <x:c r="AD10"/>
-      <x:c r="AE10"/>
-      <x:c r="AF10"/>
-      <x:c r="AG10"/>
-      <x:c r="AH10"/>
-      <x:c r="AI10" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ10" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK10" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL10" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM10" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN10" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO10"/>
-      <x:c r="AP10" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ10" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR10" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS10" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT10" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU10" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV10" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW10"/>
-      <x:c r="AX10" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY10"/>
-      <x:c r="AZ10"/>
-      <x:c r="BA10"/>
-      <x:c r="BB10"/>
-      <x:c r="BC10"/>
-      <x:c r="BD10"/>
-      <x:c r="BE10"/>
-      <x:c r="BF10"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>adamar-vlg-SCANDI_1</x:v>
-      </x:c>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Scandi</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>Гибкий мрамор «Scandi» — Лёгкий скандинавский рисунок поддерживает светлый интерьер, добавляет естественную фактуру и хорошо работает в небольших помещениях. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K10" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/21580234/kqljphlmrr8v4ftp5q7fgnc7m2x6mwxg/orig | https://avatars.mds.yandex.net/get-yastore/20811730/z2jfrv44x46kw2xnqxjdmcjlkjjkc7qt/orig | https://avatars.mds.yandex.net/get-yastore/19782553/gqwpd5z6k62dbtwxtm4dptjtf2jmqpdz/orig | https://avatars.mds.yandex.net/get-yastore/18919159/bvccxxtwvgdx2f6l9vjgxn94s2jrzrwk/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L10"/>
+      <ns0:c r="M10" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N10"/>
+      <ns0:c r="O10"/>
+      <ns0:c r="P10"/>
+      <ns0:c r="Q10" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R10" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S10"/>
+      <ns0:c r="T10"/>
+      <ns0:c r="U10"/>
+      <ns0:c r="V10" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W10" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X10" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y10" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z10" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA10"/>
+      <ns0:c r="AB10"/>
+      <ns0:c r="AC10"/>
+      <ns0:c r="AD10"/>
+      <ns0:c r="AE10"/>
+      <ns0:c r="AF10"/>
+      <ns0:c r="AG10"/>
+      <ns0:c r="AH10"/>
+      <ns0:c r="AI10" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ10" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK10" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL10" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM10" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN10" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO10"/>
+      <ns0:c r="AP10" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ10" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR10" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS10" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT10" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU10" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV10" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW10"/>
+      <ns0:c r="AX10" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY10"/>
+      <ns0:c r="AZ10"/>
+      <ns0:c r="BA10"/>
+      <ns0:c r="BB10"/>
+      <ns0:c r="BC10"/>
+      <ns0:c r="BD10"/>
+      <ns0:c r="BE10"/>
+      <ns0:c r="BF10"/>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="str">
+        <ns0:v>adamar-vlg-SCANDI_1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B11"/>
+      <ns0:c r="C11"/>
+      <ns0:c r="D11"/>
+      <ns0:c r="E11"/>
+      <ns0:c r="F11"/>
+      <ns0:c r="G11" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I11" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Scandi</ns0:v>
+      </ns0:c>
+      <ns0:c r="J11" t="str">
+        <ns0:v>Гибкий мрамор «Scandi» — Лёгкий скандинавский рисунок поддерживает светлый интерьер, добавляет естественную фактуру и хорошо работает в небольших помещениях. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -3240,123 +3240,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/21044143/9hcv6xhdxnfjrwwd98qg92wl4v5lgz6f/orig | https://avatars.mds.yandex.net/get-yastore/20274467/jsx9k6l9fsmls57rbgv52zbzcrt5zwq5/orig | https://avatars.mds.yandex.net/get-yastore/21012869/rfbzjh69f6cqw8bnk645qlv9f2vwwz8s/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zswsl6dwvnc6b8gfs6xnbcdxvxm22p5j/orig</x:v>
-      </x:c>
-      <x:c r="L11"/>
-      <x:c r="M11" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N11"/>
-      <x:c r="O11"/>
-      <x:c r="P11"/>
-      <x:c r="Q11" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R11" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S11"/>
-      <x:c r="T11"/>
-      <x:c r="U11"/>
-      <x:c r="V11" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W11" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z11" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA11"/>
-      <x:c r="AB11"/>
-      <x:c r="AC11"/>
-      <x:c r="AD11"/>
-      <x:c r="AE11"/>
-      <x:c r="AF11"/>
-      <x:c r="AG11"/>
-      <x:c r="AH11"/>
-      <x:c r="AI11" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ11" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK11" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL11" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM11" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN11" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO11"/>
-      <x:c r="AP11" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ11" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR11" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS11" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT11" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU11" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV11" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW11"/>
-      <x:c r="AX11" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY11"/>
-      <x:c r="AZ11"/>
-      <x:c r="BA11"/>
-      <x:c r="BB11"/>
-      <x:c r="BC11"/>
-      <x:c r="BD11"/>
-      <x:c r="BE11"/>
-      <x:c r="BF11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>adamar-vlg-ДУБ ВИНТАЖ</x:v>
-      </x:c>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Дуб Винтаж</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>Гибкий мрамор «Дуб Винтаж» — Фактура состаренного дерева добавляет характер и уют — подходит для интерьеров в стиле лофт, кантри и современной классики. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K11" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/21044143/9hcv6xhdxnfjrwwd98qg92wl4v5lgz6f/orig | https://avatars.mds.yandex.net/get-yastore/20274467/jsx9k6l9fsmls57rbgv52zbzcrt5zwq5/orig | https://avatars.mds.yandex.net/get-yastore/21012869/rfbzjh69f6cqw8bnk645qlv9f2vwwz8s/orig | https://avatars.mds.yandex.net/get-yastore/20274467/zswsl6dwvnc6b8gfs6xnbcdxvxm22p5j/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L11"/>
+      <ns0:c r="M11" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N11"/>
+      <ns0:c r="O11"/>
+      <ns0:c r="P11"/>
+      <ns0:c r="Q11" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R11" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S11"/>
+      <ns0:c r="T11"/>
+      <ns0:c r="U11"/>
+      <ns0:c r="V11" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W11" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X11" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y11" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z11" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA11"/>
+      <ns0:c r="AB11"/>
+      <ns0:c r="AC11"/>
+      <ns0:c r="AD11"/>
+      <ns0:c r="AE11"/>
+      <ns0:c r="AF11"/>
+      <ns0:c r="AG11"/>
+      <ns0:c r="AH11"/>
+      <ns0:c r="AI11" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ11" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK11" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL11" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM11" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN11" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO11"/>
+      <ns0:c r="AP11" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ11" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR11" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS11" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT11" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU11" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV11" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW11"/>
+      <ns0:c r="AX11" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY11"/>
+      <ns0:c r="AZ11"/>
+      <ns0:c r="BA11"/>
+      <ns0:c r="BB11"/>
+      <ns0:c r="BC11"/>
+      <ns0:c r="BD11"/>
+      <ns0:c r="BE11"/>
+      <ns0:c r="BF11"/>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" t="str">
+        <ns0:v>adamar-vlg-ДУБ ВИНТАЖ</ns0:v>
+      </ns0:c>
+      <ns0:c r="B12"/>
+      <ns0:c r="C12"/>
+      <ns0:c r="D12"/>
+      <ns0:c r="E12"/>
+      <ns0:c r="F12"/>
+      <ns0:c r="G12" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H12" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I12" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Дуб Винтаж</ns0:v>
+      </ns0:c>
+      <ns0:c r="J12" t="str">
+        <ns0:v>Гибкий мрамор «Дуб Винтаж» — Фактура состаренного дерева добавляет характер и уют — подходит для интерьеров в стиле лофт, кантри и современной классики. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -3367,123 +3367,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/20918687/wtqtqnntvvsh8zrsnh7mgg4psnkmxb7b/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mb526z5xgklm9k4529xjjs8kj8rlkckk/orig | https://avatars.mds.yandex.net/get-yastore/21044143/ftcjlr95jm5nhlr6b7tq9sknh5q4nc72/orig</x:v>
-      </x:c>
-      <x:c r="L12"/>
-      <x:c r="M12" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N12"/>
-      <x:c r="O12"/>
-      <x:c r="P12"/>
-      <x:c r="Q12" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R12" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S12"/>
-      <x:c r="T12"/>
-      <x:c r="U12"/>
-      <x:c r="V12" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W12" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z12" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA12"/>
-      <x:c r="AB12"/>
-      <x:c r="AC12"/>
-      <x:c r="AD12"/>
-      <x:c r="AE12"/>
-      <x:c r="AF12"/>
-      <x:c r="AG12"/>
-      <x:c r="AH12"/>
-      <x:c r="AI12" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ12" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK12" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL12" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM12" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN12" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO12"/>
-      <x:c r="AP12" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ12" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR12" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS12" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT12" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU12" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV12" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW12"/>
-      <x:c r="AX12" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY12"/>
-      <x:c r="AZ12"/>
-      <x:c r="BA12"/>
-      <x:c r="BB12"/>
-      <x:c r="BC12"/>
-      <x:c r="BD12"/>
-      <x:c r="BE12"/>
-      <x:c r="BF12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>adamar-vlg-BEIGE CONCRETE</x:v>
-      </x:c>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Beige Concrete</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>Гибкий мрамор «Beige Concrete» — Тёплый бежевый бетон выглядит мягче обычного серого и легко сочетается с деревом, белой сантехникой и спокойными натуральными цветами. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K12" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/20918687/wtqtqnntvvsh8zrsnh7mgg4psnkmxb7b/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mb526z5xgklm9k4529xjjs8kj8rlkckk/orig | https://avatars.mds.yandex.net/get-yastore/21044143/ftcjlr95jm5nhlr6b7tq9sknh5q4nc72/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L12"/>
+      <ns0:c r="M12" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N12"/>
+      <ns0:c r="O12"/>
+      <ns0:c r="P12"/>
+      <ns0:c r="Q12" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R12" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S12"/>
+      <ns0:c r="T12"/>
+      <ns0:c r="U12"/>
+      <ns0:c r="V12" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W12" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z12" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA12"/>
+      <ns0:c r="AB12"/>
+      <ns0:c r="AC12"/>
+      <ns0:c r="AD12"/>
+      <ns0:c r="AE12"/>
+      <ns0:c r="AF12"/>
+      <ns0:c r="AG12"/>
+      <ns0:c r="AH12"/>
+      <ns0:c r="AI12" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ12" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK12" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL12" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM12" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN12" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO12"/>
+      <ns0:c r="AP12" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ12" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR12" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS12" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT12" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU12" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV12" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW12"/>
+      <ns0:c r="AX12" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY12"/>
+      <ns0:c r="AZ12"/>
+      <ns0:c r="BA12"/>
+      <ns0:c r="BB12"/>
+      <ns0:c r="BC12"/>
+      <ns0:c r="BD12"/>
+      <ns0:c r="BE12"/>
+      <ns0:c r="BF12"/>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" t="str">
+        <ns0:v>adamar-vlg-BEIGE CONCRETE</ns0:v>
+      </ns0:c>
+      <ns0:c r="B13"/>
+      <ns0:c r="C13"/>
+      <ns0:c r="D13"/>
+      <ns0:c r="E13"/>
+      <ns0:c r="F13"/>
+      <ns0:c r="G13" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H13" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I13" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Beige Concrete</ns0:v>
+      </ns0:c>
+      <ns0:c r="J13" t="str">
+        <ns0:v>Гибкий мрамор «Beige Concrete» — Тёплый бежевый бетон выглядит мягче обычного серого и легко сочетается с деревом, белой сантехникой и спокойными натуральными цветами. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -3494,123 +3494,123 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/20760651/8qw2qwg2v87gsqggrf2qlbjll858zxkf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/zvcjwnpn7l4b6bvrxq9m5k7j87gv2w95/orig | https://avatars.mds.yandex.net/get-yastore/21012869/jv4xmtjhk8cq5zmkj2klxhg9dfrn6vlm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/f6fd5rqmkhs4r9qbjs8nb45rrqckvmlg/orig</x:v>
-      </x:c>
-      <x:c r="L13"/>
-      <x:c r="M13" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N13"/>
-      <x:c r="O13"/>
-      <x:c r="P13"/>
-      <x:c r="Q13" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R13" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S13"/>
-      <x:c r="T13"/>
-      <x:c r="U13"/>
-      <x:c r="V13" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W13" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z13" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA13"/>
-      <x:c r="AB13"/>
-      <x:c r="AC13"/>
-      <x:c r="AD13"/>
-      <x:c r="AE13"/>
-      <x:c r="AF13"/>
-      <x:c r="AG13"/>
-      <x:c r="AH13"/>
-      <x:c r="AI13" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ13" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK13" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL13" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM13" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN13" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO13"/>
-      <x:c r="AP13" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ13" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR13" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS13" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT13" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU13" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV13" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW13"/>
-      <x:c r="AX13" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY13"/>
-      <x:c r="AZ13"/>
-      <x:c r="BA13"/>
-      <x:c r="BB13"/>
-      <x:c r="BC13"/>
-      <x:c r="BD13"/>
-      <x:c r="BE13"/>
-      <x:c r="BF13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>adamar-vlg-TERRAZZO WHITE</x:v>
-      </x:c>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14" t="str">
-        <x:v>Adamar Group</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>79996244489</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>Гибкий мрамор 114×280 см — Terrazzo White</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>Гибкий мрамор «Terrazzo White» — Светлое терраццо оживляет интерьер деликатным рисунком и помогает сделать кухню, ванную или коммерческое пространство интереснее. ✨
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K13" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/20760651/8qw2qwg2v87gsqggrf2qlbjll858zxkf/orig | https://avatars.mds.yandex.net/get-yastore/21104660/zvcjwnpn7l4b6bvrxq9m5k7j87gv2w95/orig | https://avatars.mds.yandex.net/get-yastore/21012869/jv4xmtjhk8cq5zmkj2klxhg9dfrn6vlm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/f6fd5rqmkhs4r9qbjs8nb45rrqckvmlg/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L13"/>
+      <ns0:c r="M13" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N13"/>
+      <ns0:c r="O13"/>
+      <ns0:c r="P13"/>
+      <ns0:c r="Q13" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R13" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S13"/>
+      <ns0:c r="T13"/>
+      <ns0:c r="U13"/>
+      <ns0:c r="V13" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W13" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X13" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y13" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z13" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA13"/>
+      <ns0:c r="AB13"/>
+      <ns0:c r="AC13"/>
+      <ns0:c r="AD13"/>
+      <ns0:c r="AE13"/>
+      <ns0:c r="AF13"/>
+      <ns0:c r="AG13"/>
+      <ns0:c r="AH13"/>
+      <ns0:c r="AI13" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ13" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK13" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL13" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM13" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN13" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO13"/>
+      <ns0:c r="AP13" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ13" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR13" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS13" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT13" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU13" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV13" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW13"/>
+      <ns0:c r="AX13" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY13"/>
+      <ns0:c r="AZ13"/>
+      <ns0:c r="BA13"/>
+      <ns0:c r="BB13"/>
+      <ns0:c r="BC13"/>
+      <ns0:c r="BD13"/>
+      <ns0:c r="BE13"/>
+      <ns0:c r="BF13"/>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" t="str">
+        <ns0:v>adamar-vlg-TERRAZZO WHITE</ns0:v>
+      </ns0:c>
+      <ns0:c r="B14"/>
+      <ns0:c r="C14"/>
+      <ns0:c r="D14"/>
+      <ns0:c r="E14"/>
+      <ns0:c r="F14"/>
+      <ns0:c r="G14" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I14" t="str">
+        <ns0:v>Гибкий мрамор 114×280 см — Terrazzo White</ns0:v>
+      </ns0:c>
+      <ns0:c r="J14" t="str">
+        <ns0:v>Гибкий мрамор «Terrazzo White» — Светлое терраццо оживляет интерьер деликатным рисунком и помогает сделать кухню, ванную или коммерческое пространство интереснее. ✨
 Это широкоформатные панели размером 114×280 см. Один лист перекрывает большую часть стены, поэтому стыков получается меньше, а поверхность выглядит цельной. Такой материал также ищут как гибкий камень и микрокальцитные панели.
 Почему это удобно:
 • влагостойкая поверхность для внутренней отделки;
@@ -3621,217 +3621,217 @@
 ✅ Есть в наличии в Волгограде — можно забрать без ожидания поставки.
 🤝 Для дилеров и монтажных бригад действуют специальные скидки. Напишите, сколько панелей нужно, — рассчитаем условия под ваш объём.
 Подойдут для кухни, ванной, санузла, прихожей, гостиной, офиса или коммерческого помещения. В душевой зоне важно качественно герметизировать стыки и примыкания.
-📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>https://avatars.mds.yandex.net/get-yastore/21012869/zvg5c7xvfp27vb94x8dgw6nw8hrkzgs8/orig | https://avatars.mds.yandex.net/get-yastore/20900992/qf62gg7v6c79zx5nz7bbkffmx542n4ws/orig | https://avatars.mds.yandex.net/get-yastore/20900992/j8c85d75scqcql2tbc6z56sfwncft7gd/orig</x:v>
-      </x:c>
-      <x:c r="L14"/>
-      <x:c r="M14" t="str">
-        <x:v>По телефону и в сообщениях</x:v>
-      </x:c>
-      <x:c r="N14"/>
-      <x:c r="O14"/>
-      <x:c r="P14"/>
-      <x:c r="Q14" t="str">
-        <x:v>Ремонт и строительство</x:v>
-      </x:c>
-      <x:c r="R14" t="str">
-        <x:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</x:v>
-      </x:c>
-      <x:c r="S14"/>
-      <x:c r="T14"/>
-      <x:c r="U14"/>
-      <x:c r="V14" t="str">
-        <x:v>Поштучно</x:v>
-      </x:c>
-      <x:c r="W14" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="X14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z14" t="str">
-        <x:v>Штуку</x:v>
-      </x:c>
-      <x:c r="AA14"/>
-      <x:c r="AB14"/>
-      <x:c r="AC14"/>
-      <x:c r="AD14"/>
-      <x:c r="AE14"/>
-      <x:c r="AF14"/>
-      <x:c r="AG14"/>
-      <x:c r="AH14"/>
-      <x:c r="AI14" t="n">
-        <x:v>3900</x:v>
-      </x:c>
-      <x:c r="AJ14" t="str">
-        <x:v>Стройматериалы</x:v>
-      </x:c>
-      <x:c r="AK14" t="str">
-        <x:v>Товар от производителя</x:v>
-      </x:c>
-      <x:c r="AL14" t="str">
-        <x:v>Новое</x:v>
-      </x:c>
-      <x:c r="AM14" t="str">
-        <x:v>В наличии</x:v>
-      </x:c>
-      <x:c r="AN14" t="str">
-        <x:v>Отделка</x:v>
-      </x:c>
-      <x:c r="AO14"/>
-      <x:c r="AP14" t="str">
-        <x:v>Стеновые панели, рейки и элементы декора</x:v>
-      </x:c>
-      <x:c r="AQ14" t="str">
-        <x:v>Стеновые панели</x:v>
-      </x:c>
-      <x:c r="AR14" t="str">
-        <x:v>ПВХ</x:v>
-      </x:c>
-      <x:c r="AS14" t="str">
-        <x:v>Стены | Двери</x:v>
-      </x:c>
-      <x:c r="AT14" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AU14" t="n">
-        <x:v>2800</x:v>
-      </x:c>
-      <x:c r="AV14" t="n">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="AW14"/>
-      <x:c r="AX14" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AY14"/>
-      <x:c r="AZ14"/>
-      <x:c r="BA14"/>
-      <x:c r="BB14"/>
-      <x:c r="BC14"/>
-      <x:c r="BD14"/>
-      <x:c r="BE14"/>
-      <x:c r="BF14"/>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="24">
-    <x:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">
-      <x:formula1>Справочники!$D$2:$D$4</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$E$5:$E$1048576">
-      <x:formula1>Справочники!$E$2:$E$14</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$M$5:$M$1048576">
-      <x:formula1>Справочники!$M$2:$M$4</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$N$5:$N$1048576">
-      <x:formula1>Справочники!$N$2:$N$5</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$Q$5:$Q$1048576">
-      <x:formula1>Справочники!$Q$2:$Q$2</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$V$5:$V$1048576">
-      <x:formula1>Справочники!$V$2:$V$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$Z$5:$Z$1048576">
-      <x:formula1>Справочники!$Z$2:$Z$4</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AA$5:$AA$1048576">
-      <x:formula1>Справочники!$AA$2:$AA$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AH$5:$AH$1048576">
-      <x:formula1>Справочники!$AH$2:$AH$6</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AJ$5:$AJ$1048576">
-      <x:formula1>Справочники!$AJ$2:$AJ$2</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AK$5:$AK$1048576">
-      <x:formula1>Справочники!$AK$2:$AK$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AL$5:$AL$1048576">
-      <x:formula1>Справочники!$AL$2:$AL$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AM$5:$AM$1048576">
-      <x:formula1>Справочники!$AM$2:$AM$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AN$5:$AN$1048576">
-      <x:formula1>Справочники!$AN$2:$AN$2</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AP$5:$AP$1048576">
-      <x:formula1>Справочники!$AP$2:$AP$2</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AQ$5:$AQ$1048576">
-      <x:formula1>Справочники!$AQ$2:$AQ$2</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AR$5:$AR$1048576">
-      <x:formula1>Справочники!$AR$2:$AR$13</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AT$5:$AT$1048576">
-      <x:formula1>Справочники!$AT$2:$AT$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AW$5:$AW$1048576">
-      <x:formula1>Справочники!$AW$2:$AW$7</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AX$5:$AX$1048576">
-      <x:formula1>Справочники!$AX$2:$AX$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$AY$5:$AY$1048576">
-      <x:formula1>Справочники!$AY$2:$AY$3</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$BA$5:$BA$1048576">
-      <x:formula1>Справочники!$BA$2:$BA$10</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$BC$5:$BC$1048576">
-      <x:formula1>Справочники!$BC$2:$BC$14</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="1" sqref="$BD$5:$BD$1048576">
-      <x:formula1>Справочники!$BD$2:$BD$4</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY3" r:id="Rea6b878ba1584c82"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="Rffcd1e82f37243e2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA3" r:id="Ra3ff24d102ee483e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD3" r:id="Reefecc3724834ade"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE3" r:id="R7c16469b88294280"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="Rbff4240dda3c4a29"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="R9c9b0308681d46f7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="Rc676019c77dc46ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="R38bc42fc5e6f411f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="R9cae3f0627c94d45"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="Rb8bf83eb26ac4168"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="R6cc914c6221340fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="R750f17f48c3f4c26"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="R5d987a6201aa48b7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="R11a06d40f3f5477a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="R70ef320968794330"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="Reb3d61cec0664f06"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="R63a9b7d0ee9d41e0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U4" r:id="R1e263f6e6b0b4c37"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="R3cd3ee5789ab4816"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="R15808d00529649a2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y4" r:id="Rf3f871d95b374969"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="R32a1709f23334630"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="R8c81295c80754b05"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE4" r:id="Rb1634ce95d0d4720"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF4" r:id="R56aa562a92bd4d00"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG4" r:id="Ra68f4de53b444d91"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI4" r:id="Rf466549f79334c5a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO4" r:id="R05bcd72c4a254595"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU4" r:id="R77271d982ff54b0a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV4" r:id="Rfdd6dc72e7494f81"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="Re42e2875f7574ec0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB4" r:id="Rd3442b770b2144b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE4" r:id="Rfd45c17df47d49ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF4" r:id="R1a8e4adffa5f48b5"/>
-  </x:hyperlinks>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+📍 Приходите в наш шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Здесь можно посмотреть декоры вживую, сравнить фактуры и подобрать вариант под ваш интерьер. Напишите размеры стены или приезжайте — поможем рассчитать нужное количество панелей.</ns0:v>
+      </ns0:c>
+      <ns0:c r="K14" t="str">
+        <ns0:v>https://avatars.mds.yandex.net/get-yastore/21012869/zvg5c7xvfp27vb94x8dgw6nw8hrkzgs8/orig | https://avatars.mds.yandex.net/get-yastore/20900992/qf62gg7v6c79zx5nz7bbkffmx542n4ws/orig | https://avatars.mds.yandex.net/get-yastore/20900992/j8c85d75scqcql2tbc6z56sfwncft7gd/orig</ns0:v>
+      </ns0:c>
+      <ns0:c r="L14"/>
+      <ns0:c r="M14" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N14"/>
+      <ns0:c r="O14"/>
+      <ns0:c r="P14"/>
+      <ns0:c r="Q14" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R14" t="str">
+        <ns0:v>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:v>
+      </ns0:c>
+      <ns0:c r="S14"/>
+      <ns0:c r="T14"/>
+      <ns0:c r="U14"/>
+      <ns0:c r="V14" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W14" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X14" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y14" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z14" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA14"/>
+      <ns0:c r="AB14"/>
+      <ns0:c r="AC14"/>
+      <ns0:c r="AD14"/>
+      <ns0:c r="AE14"/>
+      <ns0:c r="AF14"/>
+      <ns0:c r="AG14"/>
+      <ns0:c r="AH14"/>
+      <ns0:c r="AI14" t="n">
+        <ns0:v>3900</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ14" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK14" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL14" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM14" t="str">
+        <ns0:v>В наличии</ns0:v>
+      </ns0:c>
+      <ns0:c r="AN14" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO14"/>
+      <ns0:c r="AP14" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ14" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR14" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS14" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT14" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU14" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV14" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW14"/>
+      <ns0:c r="AX14" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY14"/>
+      <ns0:c r="AZ14"/>
+      <ns0:c r="BA14"/>
+      <ns0:c r="BB14"/>
+      <ns0:c r="BC14"/>
+      <ns0:c r="BD14"/>
+      <ns0:c r="BE14"/>
+      <ns0:c r="BF14"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:dataValidations count="24">
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">
+      <ns0:formula1>Справочники!$D$2:$D$4</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$E$5:$E$1048576">
+      <ns0:formula1>Справочники!$E$2:$E$14</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$M$5:$M$1048576">
+      <ns0:formula1>Справочники!$M$2:$M$4</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$N$5:$N$1048576">
+      <ns0:formula1>Справочники!$N$2:$N$5</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$Q$5:$Q$1048576">
+      <ns0:formula1>Справочники!$Q$2:$Q$2</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$V$5:$V$1048576">
+      <ns0:formula1>Справочники!$V$2:$V$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$Z$5:$Z$1048576">
+      <ns0:formula1>Справочники!$Z$2:$Z$4</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AA$5:$AA$1048576">
+      <ns0:formula1>Справочники!$AA$2:$AA$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AH$5:$AH$1048576">
+      <ns0:formula1>Справочники!$AH$2:$AH$6</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AJ$5:$AJ$1048576">
+      <ns0:formula1>Справочники!$AJ$2:$AJ$2</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AK$5:$AK$1048576">
+      <ns0:formula1>Справочники!$AK$2:$AK$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AL$5:$AL$1048576">
+      <ns0:formula1>Справочники!$AL$2:$AL$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AM$5:$AM$1048576">
+      <ns0:formula1>Справочники!$AM$2:$AM$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AN$5:$AN$1048576">
+      <ns0:formula1>Справочники!$AN$2:$AN$2</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AP$5:$AP$1048576">
+      <ns0:formula1>Справочники!$AP$2:$AP$2</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AQ$5:$AQ$1048576">
+      <ns0:formula1>Справочники!$AQ$2:$AQ$2</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AR$5:$AR$1048576">
+      <ns0:formula1>Справочники!$AR$2:$AR$13</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AT$5:$AT$1048576">
+      <ns0:formula1>Справочники!$AT$2:$AT$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AW$5:$AW$1048576">
+      <ns0:formula1>Справочники!$AW$2:$AW$7</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AX$5:$AX$1048576">
+      <ns0:formula1>Справочники!$AX$2:$AX$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$AY$5:$AY$1048576">
+      <ns0:formula1>Справочники!$AY$2:$AY$3</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$BA$5:$BA$1048576">
+      <ns0:formula1>Справочники!$BA$2:$BA$10</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$BC$5:$BC$1048576">
+      <ns0:formula1>Справочники!$BC$2:$BC$14</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" allowBlank="1" sqref="$BD$5:$BD$1048576">
+      <ns0:formula1>Справочники!$BD$2:$BD$4</ns0:formula1>
+    </ns0:dataValidation>
+  </ns0:dataValidations>
+  <ns0:hyperlinks>
+    <ns0:hyperlink ref="AY3" ns1:id="Rea6b878ba1584c82"/>
+    <ns0:hyperlink ref="AZ3" ns1:id="Rffcd1e82f37243e2"/>
+    <ns0:hyperlink ref="BA3" ns1:id="Ra3ff24d102ee483e"/>
+    <ns0:hyperlink ref="BD3" ns1:id="Reefecc3724834ade"/>
+    <ns0:hyperlink ref="BE3" ns1:id="R7c16469b88294280"/>
+    <ns0:hyperlink ref="A4" ns1:id="Rbff4240dda3c4a29"/>
+    <ns0:hyperlink ref="B4" ns1:id="R9c9b0308681d46f7"/>
+    <ns0:hyperlink ref="C4" ns1:id="Rc676019c77dc46ea"/>
+    <ns0:hyperlink ref="F4" ns1:id="R38bc42fc5e6f411f"/>
+    <ns0:hyperlink ref="G4" ns1:id="R9cae3f0627c94d45"/>
+    <ns0:hyperlink ref="H4" ns1:id="Rb8bf83eb26ac4168"/>
+    <ns0:hyperlink ref="K4" ns1:id="R6cc914c6221340fc"/>
+    <ns0:hyperlink ref="L4" ns1:id="R750f17f48c3f4c26"/>
+    <ns0:hyperlink ref="O4" ns1:id="R5d987a6201aa48b7"/>
+    <ns0:hyperlink ref="P4" ns1:id="R11a06d40f3f5477a"/>
+    <ns0:hyperlink ref="R4" ns1:id="R70ef320968794330"/>
+    <ns0:hyperlink ref="S4" ns1:id="Reb3d61cec0664f06"/>
+    <ns0:hyperlink ref="T4" ns1:id="R63a9b7d0ee9d41e0"/>
+    <ns0:hyperlink ref="U4" ns1:id="R1e263f6e6b0b4c37"/>
+    <ns0:hyperlink ref="W4" ns1:id="R3cd3ee5789ab4816"/>
+    <ns0:hyperlink ref="X4" ns1:id="R15808d00529649a2"/>
+    <ns0:hyperlink ref="Y4" ns1:id="Rf3f871d95b374969"/>
+    <ns0:hyperlink ref="AB4" ns1:id="R32a1709f23334630"/>
+    <ns0:hyperlink ref="AD4" ns1:id="R8c81295c80754b05"/>
+    <ns0:hyperlink ref="AE4" ns1:id="Rb1634ce95d0d4720"/>
+    <ns0:hyperlink ref="AF4" ns1:id="R56aa562a92bd4d00"/>
+    <ns0:hyperlink ref="AG4" ns1:id="Ra68f4de53b444d91"/>
+    <ns0:hyperlink ref="AI4" ns1:id="Rf466549f79334c5a"/>
+    <ns0:hyperlink ref="AO4" ns1:id="R05bcd72c4a254595"/>
+    <ns0:hyperlink ref="AU4" ns1:id="R77271d982ff54b0a"/>
+    <ns0:hyperlink ref="AV4" ns1:id="Rfdd6dc72e7494f81"/>
+    <ns0:hyperlink ref="AZ4" ns1:id="Re42e2875f7574ec0"/>
+    <ns0:hyperlink ref="BB4" ns1:id="Rd3442b770b2144b9"/>
+    <ns0:hyperlink ref="BE4" ns1:id="Rfd45c17df47d49ef"/>
+    <ns0:hyperlink ref="BF4" ns1:id="R1a8e4adffa5f48b5"/>
+  </ns0:hyperlinks>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2629,7 +2629,7 @@
       <ns0:c r="V6" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W6" t="n">
+      <ns0:c r="W6">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X6" t="n">
@@ -3137,7 +3137,7 @@
       <ns0:c r="V10" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W10" t="n">
+      <ns0:c r="W10">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X10" t="n">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2502,7 +2502,7 @@
       <ns0:c r="V5" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W5" t="n">
+      <ns0:c r="W5">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X5" t="n">
@@ -2883,7 +2883,7 @@
       <ns0:c r="V8" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W8" t="n">
+      <ns0:c r="W8">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X8" t="n">
@@ -3010,7 +3010,7 @@
       <ns0:c r="V9" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W9" t="n">
+      <ns0:c r="W9">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X9" t="n">
@@ -3264,7 +3264,7 @@
       <ns0:c r="V11" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W11" t="n">
+      <ns0:c r="W11">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X11" t="n">
@@ -3391,7 +3391,7 @@
       <ns0:c r="V12" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W12" t="n">
+      <ns0:c r="W12">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X12" t="n">
@@ -3518,7 +3518,7 @@
       <ns0:c r="V13" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W13" t="n">
+      <ns0:c r="W13">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X13" t="n">
@@ -3645,7 +3645,7 @@
       <ns0:c r="V14" t="str">
         <ns0:v>Поштучно</ns0:v>
       </ns0:c>
-      <ns0:c r="W14" t="n">
+      <ns0:c r="W14">
         <ns0:v>200</ns0:v>
       </ns0:c>
       <ns0:c r="X14" t="n">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2522,8 +2522,8 @@
       <ns0:c r="AF5"/>
       <ns0:c r="AG5"/>
       <ns0:c r="AH5"/>
-      <ns0:c r="AI5" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI5">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ5" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2649,8 +2649,8 @@
       <ns0:c r="AF6"/>
       <ns0:c r="AG6"/>
       <ns0:c r="AH6"/>
-      <ns0:c r="AI6" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI6">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ6" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2776,8 +2776,8 @@
       <ns0:c r="AF7"/>
       <ns0:c r="AG7"/>
       <ns0:c r="AH7"/>
-      <ns0:c r="AI7" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI7">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ7" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2903,8 +2903,8 @@
       <ns0:c r="AF8"/>
       <ns0:c r="AG8"/>
       <ns0:c r="AH8"/>
-      <ns0:c r="AI8" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI8">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ8" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3030,8 +3030,8 @@
       <ns0:c r="AF9"/>
       <ns0:c r="AG9"/>
       <ns0:c r="AH9"/>
-      <ns0:c r="AI9" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI9">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ9" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3157,8 +3157,8 @@
       <ns0:c r="AF10"/>
       <ns0:c r="AG10"/>
       <ns0:c r="AH10"/>
-      <ns0:c r="AI10" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI10">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ10" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3284,8 +3284,8 @@
       <ns0:c r="AF11"/>
       <ns0:c r="AG11"/>
       <ns0:c r="AH11"/>
-      <ns0:c r="AI11" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI11">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ11" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3411,8 +3411,8 @@
       <ns0:c r="AF12"/>
       <ns0:c r="AG12"/>
       <ns0:c r="AH12"/>
-      <ns0:c r="AI12" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI12">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ12" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3538,8 +3538,8 @@
       <ns0:c r="AF13"/>
       <ns0:c r="AG13"/>
       <ns0:c r="AH13"/>
-      <ns0:c r="AI13" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI13">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ13" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3665,8 +3665,8 @@
       <ns0:c r="AF14"/>
       <ns0:c r="AG14"/>
       <ns0:c r="AH14"/>
-      <ns0:c r="AI14" t="n">
-        <ns0:v>3900</ns0:v>
+      <ns0:c r="AI14">
+        <ns0:v>3950</ns0:v>
       </ns0:c>
       <ns0:c r="AJ14" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3717,6 +3717,138 @@
       <ns0:c r="BD14"/>
       <ns0:c r="BE14"/>
       <ns0:c r="BF14"/>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SOTY LIGHT GRAY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B15"/>
+      <ns0:c r="C15"/>
+      <ns0:c r="D15"/>
+      <ns0:c r="E15"/>
+      <ns0:c r="F15"/>
+      <ns0:c r="G15" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H15" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J15" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/vcdsrg87hjghbb7rrqjsgg9lk4xwxfbd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/r4mxrbl2hwf49p5l4g54r4vpwrxvzgj8/orig | https://avatars.mds.yandex.net/get-yastore/20760651/hsnpdljqjs775bgcd6dksw96qvt8m2mg/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L15"/>
+      <ns0:c r="M15" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N15"/>
+      <ns0:c r="O15"/>
+      <ns0:c r="P15"/>
+      <ns0:c r="Q15" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S15"/>
+      <ns0:c r="T15"/>
+      <ns0:c r="U15"/>
+      <ns0:c r="V15" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W15">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X15" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y15" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z15" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA15"/>
+      <ns0:c r="AB15"/>
+      <ns0:c r="AC15"/>
+      <ns0:c r="AD15"/>
+      <ns0:c r="AE15"/>
+      <ns0:c r="AF15"/>
+      <ns0:c r="AG15"/>
+      <ns0:c r="AH15"/>
+      <ns0:c r="AI15">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ15" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK15" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL15" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN15" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO15"/>
+      <ns0:c r="AP15" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ15" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR15" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS15" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT15" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU15" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV15" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW15"/>
+      <ns0:c r="AX15" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY15"/>
+      <ns0:c r="AZ15"/>
+      <ns0:c r="BA15"/>
+      <ns0:c r="BB15"/>
+      <ns0:c r="BC15"/>
+      <ns0:c r="BD15"/>
+      <ns0:c r="BE15"/>
+      <ns0:c r="BF15"/>
     </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -3850,6 +3850,138 @@
       <ns0:c r="BE15"/>
       <ns0:c r="BF15"/>
     </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SOTY GRAY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B16"/>
+      <ns0:c r="C16"/>
+      <ns0:c r="D16"/>
+      <ns0:c r="E16"/>
+      <ns0:c r="F16"/>
+      <ns0:c r="G16" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H16" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J16" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/kpgrt7s5ptkwtl6j7dj59rb9hwkrwrnq/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mh6lzzxbg8wmr87qjrnd52g9qc28btrs/orig | https://avatars.mds.yandex.net/get-yastore/21012869/zr9xw2rzqbkj45skkmgmlw4zlbz8wpfr/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L16"/>
+      <ns0:c r="M16" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N16"/>
+      <ns0:c r="O16"/>
+      <ns0:c r="P16"/>
+      <ns0:c r="Q16" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S16"/>
+      <ns0:c r="T16"/>
+      <ns0:c r="U16"/>
+      <ns0:c r="V16" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W16">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X16" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y16" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z16" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA16"/>
+      <ns0:c r="AB16"/>
+      <ns0:c r="AC16"/>
+      <ns0:c r="AD16"/>
+      <ns0:c r="AE16"/>
+      <ns0:c r="AF16"/>
+      <ns0:c r="AG16"/>
+      <ns0:c r="AH16"/>
+      <ns0:c r="AI16">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ16" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK16" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL16" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN16" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO16"/>
+      <ns0:c r="AP16" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ16" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR16" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS16" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT16" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU16" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV16" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW16"/>
+      <ns0:c r="AX16" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY16"/>
+      <ns0:c r="AZ16"/>
+      <ns0:c r="BA16"/>
+      <ns0:c r="BB16"/>
+      <ns0:c r="BC16"/>
+      <ns0:c r="BD16"/>
+      <ns0:c r="BE16"/>
+      <ns0:c r="BF16"/>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">
     <ns0:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2523,7 +2523,7 @@
       <ns0:c r="AG5"/>
       <ns0:c r="AH5"/>
       <ns0:c r="AI5">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ5" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2650,7 +2650,7 @@
       <ns0:c r="AG6"/>
       <ns0:c r="AH6"/>
       <ns0:c r="AI6">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ6" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2777,7 +2777,7 @@
       <ns0:c r="AG7"/>
       <ns0:c r="AH7"/>
       <ns0:c r="AI7">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ7" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -2904,7 +2904,7 @@
       <ns0:c r="AG8"/>
       <ns0:c r="AH8"/>
       <ns0:c r="AI8">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ8" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3031,7 +3031,7 @@
       <ns0:c r="AG9"/>
       <ns0:c r="AH9"/>
       <ns0:c r="AI9">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ9" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3158,7 +3158,7 @@
       <ns0:c r="AG10"/>
       <ns0:c r="AH10"/>
       <ns0:c r="AI10">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ10" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3285,7 +3285,7 @@
       <ns0:c r="AG11"/>
       <ns0:c r="AH11"/>
       <ns0:c r="AI11">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ11" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3412,7 +3412,7 @@
       <ns0:c r="AG12"/>
       <ns0:c r="AH12"/>
       <ns0:c r="AI12">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ12" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3539,7 +3539,7 @@
       <ns0:c r="AG13"/>
       <ns0:c r="AH13"/>
       <ns0:c r="AI13">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ13" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3666,7 +3666,7 @@
       <ns0:c r="AG14"/>
       <ns0:c r="AH14"/>
       <ns0:c r="AI14">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ14" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3796,7 +3796,7 @@
       <ns0:c r="AG15"/>
       <ns0:c r="AH15"/>
       <ns0:c r="AI15">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ15" t="str">
         <ns0:v>Стройматериалы</ns0:v>
@@ -3928,7 +3928,7 @@
       <ns0:c r="AG16"/>
       <ns0:c r="AH16"/>
       <ns0:c r="AI16">
-        <ns0:v>3950</ns0:v>
+        <ns0:v>3921</ns0:v>
       </ns0:c>
       <ns0:c r="AJ16" t="str">
         <ns0:v>Стройматериалы</ns0:v>

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -3982,6 +3982,666 @@
       <ns0:c r="BE16"/>
       <ns0:c r="BF16"/>
     </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-ДУБ ТОСКАНА</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B17"/>
+      <ns0:c r="C17"/>
+      <ns0:c r="D17"/>
+      <ns0:c r="E17"/>
+      <ns0:c r="F17"/>
+      <ns0:c r="G17" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H17" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J17" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21044143/gq6tvnvv2hzmnl4ht9t68h4t5pfqmrc5/orig | https://avatars.mds.yandex.net/get-yastore/20918687/zd7zwc559bblwrw59c8wdcqv5kfgpmgd/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mg4chd67l2fkgf89lg5tgxh2mv74zd94/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L17"/>
+      <ns0:c r="M17" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N17"/>
+      <ns0:c r="O17"/>
+      <ns0:c r="P17"/>
+      <ns0:c r="Q17" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S17"/>
+      <ns0:c r="T17"/>
+      <ns0:c r="U17"/>
+      <ns0:c r="V17" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W17">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X17" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y17" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z17" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA17"/>
+      <ns0:c r="AB17"/>
+      <ns0:c r="AC17"/>
+      <ns0:c r="AD17"/>
+      <ns0:c r="AE17"/>
+      <ns0:c r="AF17"/>
+      <ns0:c r="AG17"/>
+      <ns0:c r="AH17"/>
+      <ns0:c r="AI17">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ17" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK17" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL17" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN17" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO17"/>
+      <ns0:c r="AP17" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ17" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR17" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS17" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT17" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU17" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV17" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW17"/>
+      <ns0:c r="AX17" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY17"/>
+      <ns0:c r="AZ17"/>
+      <ns0:c r="BA17"/>
+      <ns0:c r="BB17"/>
+      <ns0:c r="BC17"/>
+      <ns0:c r="BD17"/>
+      <ns0:c r="BE17"/>
+      <ns0:c r="BF17"/>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Дуб ВЕНГЕ</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B18"/>
+      <ns0:c r="C18"/>
+      <ns0:c r="D18"/>
+      <ns0:c r="E18"/>
+      <ns0:c r="F18"/>
+      <ns0:c r="G18" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H18" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J18" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21044143/ccr9kp4dn8qxz5lfbt94ngtpxnhv8xn8/orig | https://avatars.mds.yandex.net/get-yastore/20918687/szzkvp9tp5zhh2npwxfvk88hpnzfb7qb/orig | https://avatars.mds.yandex.net/get-yastore/20918687/89rm5qdrppnc4vsgpww5hzfqpfkz8hwj/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L18"/>
+      <ns0:c r="M18" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N18"/>
+      <ns0:c r="O18"/>
+      <ns0:c r="P18"/>
+      <ns0:c r="Q18" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S18"/>
+      <ns0:c r="T18"/>
+      <ns0:c r="U18"/>
+      <ns0:c r="V18" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W18">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X18" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y18" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z18" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA18"/>
+      <ns0:c r="AB18"/>
+      <ns0:c r="AC18"/>
+      <ns0:c r="AD18"/>
+      <ns0:c r="AE18"/>
+      <ns0:c r="AF18"/>
+      <ns0:c r="AG18"/>
+      <ns0:c r="AH18"/>
+      <ns0:c r="AI18">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ18" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK18" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL18" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN18" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO18"/>
+      <ns0:c r="AP18" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ18" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR18" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS18" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT18" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU18" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV18" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW18"/>
+      <ns0:c r="AX18" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY18"/>
+      <ns0:c r="AZ18"/>
+      <ns0:c r="BA18"/>
+      <ns0:c r="BB18"/>
+      <ns0:c r="BC18"/>
+      <ns0:c r="BD18"/>
+      <ns0:c r="BE18"/>
+      <ns0:c r="BF18"/>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SIENA_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B19"/>
+      <ns0:c r="C19"/>
+      <ns0:c r="D19"/>
+      <ns0:c r="E19"/>
+      <ns0:c r="F19"/>
+      <ns0:c r="G19" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H19" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J19" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21055393/pjtzf4v2ggn2jxf82mp8lqzlvlldscds/orig | https://avatars.mds.yandex.net/get-yastore/21055393/xcf2khnk2t24n6gnm2vfd9ngqbmwpvbk/orig | https://avatars.mds.yandex.net/get-yastore/21055393/xzdmtpdldr9v6rgb8lsjq8v8bf4rtvm5/orig | https://avatars.mds.yandex.net/get-yastore/20274467/f5vddlgqd8qvnlh57ckqfc7wgbtjnjkz/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L19"/>
+      <ns0:c r="M19" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N19"/>
+      <ns0:c r="O19"/>
+      <ns0:c r="P19"/>
+      <ns0:c r="Q19" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S19"/>
+      <ns0:c r="T19"/>
+      <ns0:c r="U19"/>
+      <ns0:c r="V19" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W19">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X19" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y19" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z19" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA19"/>
+      <ns0:c r="AB19"/>
+      <ns0:c r="AC19"/>
+      <ns0:c r="AD19"/>
+      <ns0:c r="AE19"/>
+      <ns0:c r="AF19"/>
+      <ns0:c r="AG19"/>
+      <ns0:c r="AH19"/>
+      <ns0:c r="AI19">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ19" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK19" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL19" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN19" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO19"/>
+      <ns0:c r="AP19" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ19" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR19" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS19" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT19" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU19" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV19" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW19"/>
+      <ns0:c r="AX19" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY19"/>
+      <ns0:c r="AZ19"/>
+      <ns0:c r="BA19"/>
+      <ns0:c r="BB19"/>
+      <ns0:c r="BC19"/>
+      <ns0:c r="BD19"/>
+      <ns0:c r="BE19"/>
+      <ns0:c r="BF19"/>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-MILANO_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B20"/>
+      <ns0:c r="C20"/>
+      <ns0:c r="D20"/>
+      <ns0:c r="E20"/>
+      <ns0:c r="F20"/>
+      <ns0:c r="G20" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H20" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J20" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21055393/kpbckqnvj9tcxkv52ghp294zxplqctsw/orig | https://avatars.mds.yandex.net/get-yastore/20918687/v78snp6r8vvcqjg6dx4vndhbfbl6gvqn/orig | https://avatars.mds.yandex.net/get-yastore/20918687/86gvwsn2bgr7stcvwcrxjpx5ljjk6nld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/dwpwsscw86tqq958wmbjc8hpzsp92cbf/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L20"/>
+      <ns0:c r="M20" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N20"/>
+      <ns0:c r="O20"/>
+      <ns0:c r="P20"/>
+      <ns0:c r="Q20" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S20"/>
+      <ns0:c r="T20"/>
+      <ns0:c r="U20"/>
+      <ns0:c r="V20" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W20">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X20" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y20" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z20" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA20"/>
+      <ns0:c r="AB20"/>
+      <ns0:c r="AC20"/>
+      <ns0:c r="AD20"/>
+      <ns0:c r="AE20"/>
+      <ns0:c r="AF20"/>
+      <ns0:c r="AG20"/>
+      <ns0:c r="AH20"/>
+      <ns0:c r="AI20">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ20" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK20" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL20" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN20" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO20"/>
+      <ns0:c r="AP20" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ20" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR20" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS20" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT20" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU20" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV20" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW20"/>
+      <ns0:c r="AX20" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY20"/>
+      <ns0:c r="AZ20"/>
+      <ns0:c r="BA20"/>
+      <ns0:c r="BB20"/>
+      <ns0:c r="BC20"/>
+      <ns0:c r="BD20"/>
+      <ns0:c r="BE20"/>
+      <ns0:c r="BF20"/>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-FONDAMENTO_DECOR_2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B21"/>
+      <ns0:c r="C21"/>
+      <ns0:c r="D21"/>
+      <ns0:c r="E21"/>
+      <ns0:c r="F21"/>
+      <ns0:c r="G21" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H21" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J21" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Гибкий мрамор для стен, 1140х2800 мм» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/ljdlf7jj44xvmtzkm8nzzdpql6m64x5l/orig | https://avatars.mds.yandex.net/get-yastore/20274467/8svljtp6jjcrd7s79x7l6mx84ft582xb/orig | https://avatars.mds.yandex.net/get-yastore/21012869/x68jbrttlkgfg2tx9zf9lzmxfg65wcnl/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L21"/>
+      <ns0:c r="M21" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N21"/>
+      <ns0:c r="O21"/>
+      <ns0:c r="P21"/>
+      <ns0:c r="Q21" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S21"/>
+      <ns0:c r="T21"/>
+      <ns0:c r="U21"/>
+      <ns0:c r="V21" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W21">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X21" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y21" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z21" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA21"/>
+      <ns0:c r="AB21"/>
+      <ns0:c r="AC21"/>
+      <ns0:c r="AD21"/>
+      <ns0:c r="AE21"/>
+      <ns0:c r="AF21"/>
+      <ns0:c r="AG21"/>
+      <ns0:c r="AH21"/>
+      <ns0:c r="AI21">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ21" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK21" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL21" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN21" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO21"/>
+      <ns0:c r="AP21" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ21" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR21" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS21" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT21" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU21" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV21" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW21"/>
+      <ns0:c r="AX21" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY21"/>
+      <ns0:c r="AZ21"/>
+      <ns0:c r="BA21"/>
+      <ns0:c r="BB21"/>
+      <ns0:c r="BC21"/>
+      <ns0:c r="BD21"/>
+      <ns0:c r="BE21"/>
+      <ns0:c r="BF21"/>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">
     <ns0:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -2463,8 +2463,10 @@
       <ns0:c r="H5" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I5" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — WHITE CONCRETE</ns0:v>
+      <ns0:c r="I5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — WHITE CONCRETE</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J5" t="str">
         <ns0:v>Гибкий мрамор «WHITE CONCRETE» — Светлый бетонный рисунок выглядит современно и не перегружает интерьер — хороший фон для минимализма, лофта и спокойных светлых пространств. ✨
@@ -2590,8 +2592,10 @@
       <ns0:c r="H6" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I6" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Дуб Сонома</ns0:v>
+      <ns0:c r="I6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Дуб Сонома</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J6" t="str">
         <ns0:v>Гибкий мрамор «Дуб Сонома» — Тёплая древесная фактура добавляет интерьеру уюта и хорошо сочетается со светлой мебелью, спокойными стенами и натуральными оттенками. ✨
@@ -2717,8 +2721,10 @@
       <ns0:c r="H7" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I7" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — White Concrete Fon</ns0:v>
+      <ns0:c r="I7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — White Concrete Fon</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J7" t="str">
         <ns0:v>Гибкий мрамор «White Concrete Fon» — Мягкий светлый бетон создаёт аккуратный нейтральный фон и визуально делает пространство легче — особенно удачно смотрится в кухне и ванной. ✨
@@ -2844,8 +2850,10 @@
       <ns0:c r="H8" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I8" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Grey Lord</ns0:v>
+      <ns0:c r="I8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Grey Lord</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J8" t="str">
         <ns0:v>Гибкий мрамор «Grey Lord» — Выразительный серый камень помогает собрать строгий современный интерьер и подходит для акцентной стены без лишней пестроты. ✨
@@ -2971,8 +2979,10 @@
       <ns0:c r="H9" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I9" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — White Rock</ns0:v>
+      <ns0:c r="I9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — White Rock</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J9" t="str">
         <ns0:v>Гибкий мрамор «White Rock» — Светлая каменная текстура освежает помещение и даёт эффект цельной дорогой отделки, сохраняя спокойную цветовую гамму. ✨
@@ -3098,8 +3108,10 @@
       <ns0:c r="H10" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I10" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Орех тёмный</ns0:v>
+      <ns0:c r="I10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Орех тёмный</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J10" t="str">
         <ns0:v>Гибкий мрамор «Орех тёмный» — Глубокий древесный оттенок делает интерьер теплее и солиднее — красивое решение для кабинета, спальни, прихожей или акцентной стены. ✨
@@ -3225,8 +3237,10 @@
       <ns0:c r="H11" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I11" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Scandi</ns0:v>
+      <ns0:c r="I11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Scandi</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J11" t="str">
         <ns0:v>Гибкий мрамор «Scandi» — Лёгкий скандинавский рисунок поддерживает светлый интерьер, добавляет естественную фактуру и хорошо работает в небольших помещениях. ✨
@@ -3352,8 +3366,10 @@
       <ns0:c r="H12" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I12" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Дуб Винтаж</ns0:v>
+      <ns0:c r="I12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Дуб Винтаж</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J12" t="str">
         <ns0:v>Гибкий мрамор «Дуб Винтаж» — Фактура состаренного дерева добавляет характер и уют — подходит для интерьеров в стиле лофт, кантри и современной классики. ✨
@@ -3479,8 +3495,10 @@
       <ns0:c r="H13" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I13" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Beige Concrete</ns0:v>
+      <ns0:c r="I13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Beige Concrete</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J13" t="str">
         <ns0:v>Гибкий мрамор «Beige Concrete» — Тёплый бежевый бетон выглядит мягче обычного серого и легко сочетается с деревом, белой сантехникой и спокойными натуральными цветами. ✨
@@ -3606,8 +3624,10 @@
       <ns0:c r="H14" t="str">
         <ns0:v>79996244489</ns0:v>
       </ns0:c>
-      <ns0:c r="I14" t="str">
-        <ns0:v>Гибкий мрамор 114×280 см — Terrazzo White</ns0:v>
+      <ns0:c r="I14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Terrazzo White</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="J14" t="str">
         <ns0:v>Гибкий мрамор «Terrazzo White» — Светлое терраццо оживляет интерьер деликатным рисунком и помогает сделать кухню, ванную или коммерческое пространство интереснее. ✨
@@ -3737,7 +3757,7 @@
       </ns0:c>
       <ns0:c r="I15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — SOTY LIGHT GRAY</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J15" t="inlineStr">
@@ -3869,7 +3889,7 @@
       </ns0:c>
       <ns0:c r="I16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — SOTY GRAY</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J16" t="inlineStr">
@@ -4001,7 +4021,7 @@
       </ns0:c>
       <ns0:c r="I17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — ДУБ ТОСКАНА</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J17" t="inlineStr">
@@ -4133,7 +4153,7 @@
       </ns0:c>
       <ns0:c r="I18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — Дуб ВЕНГЕ</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J18" t="inlineStr">
@@ -4265,7 +4285,7 @@
       </ns0:c>
       <ns0:c r="I19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — SIENA 1</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J19" t="inlineStr">
@@ -4397,7 +4417,7 @@
       </ns0:c>
       <ns0:c r="I20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — MILANO 1</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J20" t="inlineStr">
@@ -4529,7 +4549,7 @@
       </ns0:c>
       <ns0:c r="I21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Гибкий мрамор для стен, 1140х2800 мм</ns0:t>
+          <ns0:t>Гибкий мрамор 114х280 см — FONDAMENTO DECOR 2</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J21" t="inlineStr">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -4662,6 +4662,1326 @@
       <ns0:c r="BE21"/>
       <ns0:c r="BF21"/>
     </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Diagonal Wood</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B22"/>
+      <ns0:c r="C22"/>
+      <ns0:c r="D22"/>
+      <ns0:c r="E22"/>
+      <ns0:c r="F22"/>
+      <ns0:c r="G22" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H22" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Diagonal Wood</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J22" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Diagonal Wood» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20900992/8rr4hmg2ccgglvmmfrsv4j6xsvxhr2tc/orig | https://avatars.mds.yandex.net/get-yastore/20900992/dz64p4phw87hprkkwtxfsgk7m2fgvcqm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/ld56wsf2t6f9wpct7px28bvwtqxp7wc5/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L22"/>
+      <ns0:c r="M22" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N22"/>
+      <ns0:c r="O22"/>
+      <ns0:c r="P22"/>
+      <ns0:c r="Q22" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S22"/>
+      <ns0:c r="T22"/>
+      <ns0:c r="U22"/>
+      <ns0:c r="V22" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W22">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X22" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y22" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z22" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA22"/>
+      <ns0:c r="AB22"/>
+      <ns0:c r="AC22"/>
+      <ns0:c r="AD22"/>
+      <ns0:c r="AE22"/>
+      <ns0:c r="AF22"/>
+      <ns0:c r="AG22"/>
+      <ns0:c r="AH22"/>
+      <ns0:c r="AI22">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ22" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK22" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL22" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN22" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO22"/>
+      <ns0:c r="AP22" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ22" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR22" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS22" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT22" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU22" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV22" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW22"/>
+      <ns0:c r="AX22" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY22"/>
+      <ns0:c r="AZ22"/>
+      <ns0:c r="BA22"/>
+      <ns0:c r="BB22"/>
+      <ns0:c r="BC22"/>
+      <ns0:c r="BD22"/>
+      <ns0:c r="BE22"/>
+      <ns0:c r="BF22"/>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-BETON FERONI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B23"/>
+      <ns0:c r="C23"/>
+      <ns0:c r="D23"/>
+      <ns0:c r="E23"/>
+      <ns0:c r="F23"/>
+      <ns0:c r="G23" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H23" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — BETON FERONI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J23" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «BETON FERONI» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/q775nsnhfv9dfb2486f2f9qtd9rmffpb/orig | https://avatars.mds.yandex.net/get-yastore/20918687/q5ttswrk7xrxnfn6z4c9x9wp2hfxs566/orig | https://avatars.mds.yandex.net/get-yastore/21055393/77zplgmjgc72rls96628pdkfckft46dp/orig | https://avatars.mds.yandex.net/get-yastore/20760651/wdk2qsr69dxrvvtkjxccs5gslllbnzkc/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L23"/>
+      <ns0:c r="M23" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N23"/>
+      <ns0:c r="O23"/>
+      <ns0:c r="P23"/>
+      <ns0:c r="Q23" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S23"/>
+      <ns0:c r="T23"/>
+      <ns0:c r="U23"/>
+      <ns0:c r="V23" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W23">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X23" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y23" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z23" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA23"/>
+      <ns0:c r="AB23"/>
+      <ns0:c r="AC23"/>
+      <ns0:c r="AD23"/>
+      <ns0:c r="AE23"/>
+      <ns0:c r="AF23"/>
+      <ns0:c r="AG23"/>
+      <ns0:c r="AH23"/>
+      <ns0:c r="AI23">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ23" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK23" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL23" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN23" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO23"/>
+      <ns0:c r="AP23" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ23" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR23" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS23" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT23" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU23" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV23" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW23"/>
+      <ns0:c r="AX23" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY23"/>
+      <ns0:c r="AZ23"/>
+      <ns0:c r="BA23"/>
+      <ns0:c r="BB23"/>
+      <ns0:c r="BC23"/>
+      <ns0:c r="BD23"/>
+      <ns0:c r="BE23"/>
+      <ns0:c r="BF23"/>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-COLORED MARBLE 7</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B24"/>
+      <ns0:c r="C24"/>
+      <ns0:c r="D24"/>
+      <ns0:c r="E24"/>
+      <ns0:c r="F24"/>
+      <ns0:c r="G24" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H24" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — COLORED MARBLE 7</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J24" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «COLORED MARBLE 7» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/zrcg6w7hg548jtbwpd6lb5qv95plg5hw/orig | https://avatars.mds.yandex.net/get-yastore/20274467/gdmk94hv9bwkq7fpmsxqcvbpkflczrxt/orig | https://avatars.mds.yandex.net/get-yastore/20274467/wp28gth8f8h9bjdw9n9jz55c8xkrqrnx/orig | https://avatars.mds.yandex.net/get-yastore/20274467/r2p69stwgdp78tcw5fsnngrb5l72fkb9/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L24"/>
+      <ns0:c r="M24" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N24"/>
+      <ns0:c r="O24"/>
+      <ns0:c r="P24"/>
+      <ns0:c r="Q24" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S24"/>
+      <ns0:c r="T24"/>
+      <ns0:c r="U24"/>
+      <ns0:c r="V24" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W24">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X24" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y24" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z24" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA24"/>
+      <ns0:c r="AB24"/>
+      <ns0:c r="AC24"/>
+      <ns0:c r="AD24"/>
+      <ns0:c r="AE24"/>
+      <ns0:c r="AF24"/>
+      <ns0:c r="AG24"/>
+      <ns0:c r="AH24"/>
+      <ns0:c r="AI24">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ24" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK24" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL24" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN24" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO24"/>
+      <ns0:c r="AP24" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ24" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR24" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS24" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT24" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU24" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV24" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW24"/>
+      <ns0:c r="AX24" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY24"/>
+      <ns0:c r="AZ24"/>
+      <ns0:c r="BA24"/>
+      <ns0:c r="BB24"/>
+      <ns0:c r="BC24"/>
+      <ns0:c r="BD24"/>
+      <ns0:c r="BE24"/>
+      <ns0:c r="BF24"/>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_Vanila_Sky</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B25"/>
+      <ns0:c r="C25"/>
+      <ns0:c r="D25"/>
+      <ns0:c r="E25"/>
+      <ns0:c r="F25"/>
+      <ns0:c r="G25" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H25" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy Vanila Sky</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J25" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy Vanila Sky» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20274467/4zjf6j8qllw66k8mc2kjkpkrzbtpdvhx/orig | https://avatars.mds.yandex.net/get-yastore/20918687/t6ll57zcx7swtqkgrsshnhplcsb8qx7n/orig | https://avatars.mds.yandex.net/get-yastore/21055393/cjs7kt22xn4n5dctndxkkr47hl76bv29/orig | https://avatars.mds.yandex.net/get-yastore/18125838/bw72zxhq46m5s5rb6dbnsln7cdpbwkp2/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L25"/>
+      <ns0:c r="M25" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N25"/>
+      <ns0:c r="O25"/>
+      <ns0:c r="P25"/>
+      <ns0:c r="Q25" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S25"/>
+      <ns0:c r="T25"/>
+      <ns0:c r="U25"/>
+      <ns0:c r="V25" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W25">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X25" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y25" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z25" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA25"/>
+      <ns0:c r="AB25"/>
+      <ns0:c r="AC25"/>
+      <ns0:c r="AD25"/>
+      <ns0:c r="AE25"/>
+      <ns0:c r="AF25"/>
+      <ns0:c r="AG25"/>
+      <ns0:c r="AH25"/>
+      <ns0:c r="AI25">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ25" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK25" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL25" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN25" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO25"/>
+      <ns0:c r="AP25" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ25" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR25" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS25" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT25" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU25" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV25" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW25"/>
+      <ns0:c r="AX25" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY25"/>
+      <ns0:c r="AZ25"/>
+      <ns0:c r="BA25"/>
+      <ns0:c r="BB25"/>
+      <ns0:c r="BC25"/>
+      <ns0:c r="BD25"/>
+      <ns0:c r="BE25"/>
+      <ns0:c r="BF25"/>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-SCRIBBLE GRAY_1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B26"/>
+      <ns0:c r="C26"/>
+      <ns0:c r="D26"/>
+      <ns0:c r="E26"/>
+      <ns0:c r="F26"/>
+      <ns0:c r="G26" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H26" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — SCRIBBLE GRAY 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J26" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «SCRIBBLE GRAY 1» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21055393/9kkt59pv4mdn66w5bq7ts4s5s2zwvdcl/orig | https://avatars.mds.yandex.net/get-yastore/21055393/v89g7vkm4fpkcph8q5576xhg95kcchld/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jfwnzj7czzdm72hsftfvfk5pzpwnjj2b/orig | https://avatars.mds.yandex.net/get-yastore/21055393/bk2tdvhntmz7zl25g9pzsxx2clkzxmwx/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L26"/>
+      <ns0:c r="M26" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N26"/>
+      <ns0:c r="O26"/>
+      <ns0:c r="P26"/>
+      <ns0:c r="Q26" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S26"/>
+      <ns0:c r="T26"/>
+      <ns0:c r="U26"/>
+      <ns0:c r="V26" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W26">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X26" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y26" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z26" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA26"/>
+      <ns0:c r="AB26"/>
+      <ns0:c r="AC26"/>
+      <ns0:c r="AD26"/>
+      <ns0:c r="AE26"/>
+      <ns0:c r="AF26"/>
+      <ns0:c r="AG26"/>
+      <ns0:c r="AH26"/>
+      <ns0:c r="AI26">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ26" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK26" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL26" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN26" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO26"/>
+      <ns0:c r="AP26" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ26" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR26" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS26" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT26" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU26" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV26" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW26"/>
+      <ns0:c r="AX26" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY26"/>
+      <ns0:c r="AZ26"/>
+      <ns0:c r="BA26"/>
+      <ns0:c r="BB26"/>
+      <ns0:c r="BC26"/>
+      <ns0:c r="BD26"/>
+      <ns0:c r="BE26"/>
+      <ns0:c r="BF26"/>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_ Emperador Gold</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B27"/>
+      <ns0:c r="C27"/>
+      <ns0:c r="D27"/>
+      <ns0:c r="E27"/>
+      <ns0:c r="F27"/>
+      <ns0:c r="G27" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H27" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy  Emperador Gold</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J27" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy  Emperador Gold» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20760651/g8zk8w4pxtbvqw4kv4pdcbp9rjqj6rxm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/s9z96jw5d2bwd5pwvpwp7rzmxn4j7nx9/orig | https://avatars.mds.yandex.net/get-yastore/20760651/hs5zlsdcqp92f54bvt7scfmdfx6p9bzm/orig | https://avatars.mds.yandex.net/get-yastore/20760651/cgwq5zxnjsnwnpnrc8cn7d8brfwx96pp/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L27"/>
+      <ns0:c r="M27" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N27"/>
+      <ns0:c r="O27"/>
+      <ns0:c r="P27"/>
+      <ns0:c r="Q27" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S27"/>
+      <ns0:c r="T27"/>
+      <ns0:c r="U27"/>
+      <ns0:c r="V27" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W27">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X27" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y27" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z27" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA27"/>
+      <ns0:c r="AB27"/>
+      <ns0:c r="AC27"/>
+      <ns0:c r="AD27"/>
+      <ns0:c r="AE27"/>
+      <ns0:c r="AF27"/>
+      <ns0:c r="AG27"/>
+      <ns0:c r="AH27"/>
+      <ns0:c r="AI27">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ27" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK27" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL27" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM27" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN27" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO27"/>
+      <ns0:c r="AP27" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ27" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR27" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS27" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT27" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU27" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV27" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW27"/>
+      <ns0:c r="AX27" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY27"/>
+      <ns0:c r="AZ27"/>
+      <ns0:c r="BA27"/>
+      <ns0:c r="BB27"/>
+      <ns0:c r="BC27"/>
+      <ns0:c r="BD27"/>
+      <ns0:c r="BE27"/>
+      <ns0:c r="BF27"/>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Onyx Sonara_1RESCALE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B28"/>
+      <ns0:c r="C28"/>
+      <ns0:c r="D28"/>
+      <ns0:c r="E28"/>
+      <ns0:c r="F28"/>
+      <ns0:c r="G28" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H28" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Onyx Sonara 1RESCALE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J28" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Onyx Sonara 1RESCALE» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21055393/dlshdvlqg4tlg6rtvlcvm8p8ktt99c9f/orig | https://avatars.mds.yandex.net/get-yastore/20918687/mr4n22wvwmjmmp4pg6n4bpqkkcpc28jf/orig | https://avatars.mds.yandex.net/get-yastore/20918687/489478v5kpn5hqncffc4fn7lcmxttlmf/orig | https://avatars.mds.yandex.net/get-yastore/20918687/qjdnd5cbc5pv5lqx7rtgph64mpwsmvrw/orig | https://avatars.mds.yandex.net/get-yastore/20918687/jhnhd8x8m4kgccgtkr9kql8h2mqjzf42/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L28"/>
+      <ns0:c r="M28" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N28"/>
+      <ns0:c r="O28"/>
+      <ns0:c r="P28"/>
+      <ns0:c r="Q28" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S28"/>
+      <ns0:c r="T28"/>
+      <ns0:c r="U28"/>
+      <ns0:c r="V28" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W28">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X28" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y28" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z28" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA28"/>
+      <ns0:c r="AB28"/>
+      <ns0:c r="AC28"/>
+      <ns0:c r="AD28"/>
+      <ns0:c r="AE28"/>
+      <ns0:c r="AF28"/>
+      <ns0:c r="AG28"/>
+      <ns0:c r="AH28"/>
+      <ns0:c r="AI28">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ28" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK28" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL28" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM28" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN28" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO28"/>
+      <ns0:c r="AP28" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ28" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR28" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS28" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT28" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU28" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV28" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW28"/>
+      <ns0:c r="AX28" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY28"/>
+      <ns0:c r="AZ28"/>
+      <ns0:c r="BA28"/>
+      <ns0:c r="BB28"/>
+      <ns0:c r="BC28"/>
+      <ns0:c r="BD28"/>
+      <ns0:c r="BE28"/>
+      <ns0:c r="BF28"/>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Tile Wood</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B29"/>
+      <ns0:c r="C29"/>
+      <ns0:c r="D29"/>
+      <ns0:c r="E29"/>
+      <ns0:c r="F29"/>
+      <ns0:c r="G29" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H29" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I29" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Tile Wood</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J29" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Tile Wood» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K29" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20900992/tgk654kbhhjcm7h45nqnr2gg962p6677/orig | https://avatars.mds.yandex.net/get-yastore/20900992/gpkckjhdffg525crqsz9scntw9bf5kwj/orig | https://avatars.mds.yandex.net/get-yastore/20900992/kl9x9jrkl7z7lqxkmsxlm5nfql88zc8b/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L29"/>
+      <ns0:c r="M29" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N29"/>
+      <ns0:c r="O29"/>
+      <ns0:c r="P29"/>
+      <ns0:c r="Q29" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R29" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S29"/>
+      <ns0:c r="T29"/>
+      <ns0:c r="U29"/>
+      <ns0:c r="V29" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W29">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X29" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y29" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z29" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA29"/>
+      <ns0:c r="AB29"/>
+      <ns0:c r="AC29"/>
+      <ns0:c r="AD29"/>
+      <ns0:c r="AE29"/>
+      <ns0:c r="AF29"/>
+      <ns0:c r="AG29"/>
+      <ns0:c r="AH29"/>
+      <ns0:c r="AI29">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ29" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK29" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL29" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM29" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN29" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO29"/>
+      <ns0:c r="AP29" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ29" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR29" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS29" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT29" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU29" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV29" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW29"/>
+      <ns0:c r="AX29" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY29"/>
+      <ns0:c r="AZ29"/>
+      <ns0:c r="BA29"/>
+      <ns0:c r="BB29"/>
+      <ns0:c r="BC29"/>
+      <ns0:c r="BD29"/>
+      <ns0:c r="BE29"/>
+      <ns0:c r="BF29"/>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-BETON GREYSON_2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B30"/>
+      <ns0:c r="C30"/>
+      <ns0:c r="D30"/>
+      <ns0:c r="E30"/>
+      <ns0:c r="F30"/>
+      <ns0:c r="G30" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H30" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I30" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — BETON GREYSON 2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J30" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «BETON GREYSON 2» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K30" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/d8c667nvxvfrknpnsnbc5dqlclssppfm/orig | https://avatars.mds.yandex.net/get-yastore/20274467/x95jrn2jjbtlqk4lrdptcsf7p8fbmgrs/orig | https://avatars.mds.yandex.net/get-yastore/20274467/shmhnrqg5gbtwl994l2rlprv2tg27mb7/orig | https://avatars.mds.yandex.net/get-yastore/20918687/vfcwt5qh4nlsz6npz6td9hxpxqpbcccz/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L30"/>
+      <ns0:c r="M30" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N30"/>
+      <ns0:c r="O30"/>
+      <ns0:c r="P30"/>
+      <ns0:c r="Q30" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R30" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S30"/>
+      <ns0:c r="T30"/>
+      <ns0:c r="U30"/>
+      <ns0:c r="V30" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W30">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X30" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y30" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z30" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA30"/>
+      <ns0:c r="AB30"/>
+      <ns0:c r="AC30"/>
+      <ns0:c r="AD30"/>
+      <ns0:c r="AE30"/>
+      <ns0:c r="AF30"/>
+      <ns0:c r="AG30"/>
+      <ns0:c r="AH30"/>
+      <ns0:c r="AI30">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ30" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK30" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL30" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM30" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN30" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO30"/>
+      <ns0:c r="AP30" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ30" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR30" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS30" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT30" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU30" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV30" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW30"/>
+      <ns0:c r="AX30" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY30"/>
+      <ns0:c r="AZ30"/>
+      <ns0:c r="BA30"/>
+      <ns0:c r="BB30"/>
+      <ns0:c r="BC30"/>
+      <ns0:c r="BD30"/>
+      <ns0:c r="BE30"/>
+      <ns0:c r="BF30"/>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Glossy_ColoredMarble_12</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B31"/>
+      <ns0:c r="C31"/>
+      <ns0:c r="D31"/>
+      <ns0:c r="E31"/>
+      <ns0:c r="F31"/>
+      <ns0:c r="G31" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H31" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Glossy ColoredMarble 12</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J31" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Glossy ColoredMarble 12» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/20918687/mqnvdhj4pf7xszrl94qz75mxk47n9tjd/orig | https://avatars.mds.yandex.net/get-yastore/20811730/95dwnhrcxkhbg6nzbb4wl5r95zmtrb54/orig | https://avatars.mds.yandex.net/get-yastore/21580234/5dg2vv677zl8rlt75nx5s9zzh2hr5fhz/orig | https://avatars.mds.yandex.net/get-yastore/18125838/h2k7jt5f775hrbcx6xtl2p5dbp6m2642/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L31"/>
+      <ns0:c r="M31" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N31"/>
+      <ns0:c r="O31"/>
+      <ns0:c r="P31"/>
+      <ns0:c r="Q31" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S31"/>
+      <ns0:c r="T31"/>
+      <ns0:c r="U31"/>
+      <ns0:c r="V31" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W31">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X31" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y31" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z31" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA31"/>
+      <ns0:c r="AB31"/>
+      <ns0:c r="AC31"/>
+      <ns0:c r="AD31"/>
+      <ns0:c r="AE31"/>
+      <ns0:c r="AF31"/>
+      <ns0:c r="AG31"/>
+      <ns0:c r="AH31"/>
+      <ns0:c r="AI31">
+        <ns0:v>3950</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ31" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK31" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL31" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM31" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN31" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO31"/>
+      <ns0:c r="AP31" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ31" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR31" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS31" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT31" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU31" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV31" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW31"/>
+      <ns0:c r="AX31" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY31"/>
+      <ns0:c r="AZ31"/>
+      <ns0:c r="BA31"/>
+      <ns0:c r="BB31"/>
+      <ns0:c r="BC31"/>
+      <ns0:c r="BD31"/>
+      <ns0:c r="BE31"/>
+      <ns0:c r="BF31"/>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">
     <ns0:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">

--- a/avito.xlsx
+++ b/avito.xlsx
@@ -5982,6 +5982,138 @@
       <ns0:c r="BE31"/>
       <ns0:c r="BF31"/>
     </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>adamar-vlg-Жидкие гвозди_290мл</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B32"/>
+      <ns0:c r="C32"/>
+      <ns0:c r="D32"/>
+      <ns0:c r="E32"/>
+      <ns0:c r="F32"/>
+      <ns0:c r="G32" t="str">
+        <ns0:v>Adamar Group</ns0:v>
+      </ns0:c>
+      <ns0:c r="H32" t="str">
+        <ns0:v>79996244489</ns0:v>
+      </ns0:c>
+      <ns0:c r="I32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Гибкий мрамор 114х280 см — Жидкие гвозди 290мл</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J32" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Гибкий мрамор «Жидкие гвозди 290мл» — выразительная отделка для современного интерьера ✨
+Это широкоформатные панели 114×280 см, которые также называют гибким камнем и микрокальцитными панелями. Материал подходит для кухни, ванной, прихожей, гостиной, офиса и коммерческих помещений. Панели легко режутся и быстро монтируются на прочное основание.
+✅ Есть в наличии в Волгограде.
+🤝 Дилерам и монтажным бригадам предоставляем специальные скидки.
+📍 Приходите в шоурум: ТЦ «Новосрой», 2 этаж, г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3. Посмотрите декоры вживую и получите расчёт количества панелей.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://avatars.mds.yandex.net/get-yastore/21012869/rb8t5498jj2657gnvgwbv4gnzgcvhwx4/orig</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L32"/>
+      <ns0:c r="M32" t="str">
+        <ns0:v>По телефону и в сообщениях</ns0:v>
+      </ns0:c>
+      <ns0:c r="N32"/>
+      <ns0:c r="O32"/>
+      <ns0:c r="P32"/>
+      <ns0:c r="Q32" t="str">
+        <ns0:v>Ремонт и строительство</ns0:v>
+      </ns0:c>
+      <ns0:c r="R32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>г. Волгоград, ул. 25-летия Октября, д. 1, стр. 3</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S32"/>
+      <ns0:c r="T32"/>
+      <ns0:c r="U32"/>
+      <ns0:c r="V32" t="str">
+        <ns0:v>Поштучно</ns0:v>
+      </ns0:c>
+      <ns0:c r="W32">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="X32" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Y32" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="Z32" t="str">
+        <ns0:v>Штуку</ns0:v>
+      </ns0:c>
+      <ns0:c r="AA32"/>
+      <ns0:c r="AB32"/>
+      <ns0:c r="AC32"/>
+      <ns0:c r="AD32"/>
+      <ns0:c r="AE32"/>
+      <ns0:c r="AF32"/>
+      <ns0:c r="AG32"/>
+      <ns0:c r="AH32"/>
+      <ns0:c r="AI32">
+        <ns0:v>490</ns0:v>
+      </ns0:c>
+      <ns0:c r="AJ32" t="str">
+        <ns0:v>Стройматериалы</ns0:v>
+      </ns0:c>
+      <ns0:c r="AK32" t="str">
+        <ns0:v>Товар от производителя</ns0:v>
+      </ns0:c>
+      <ns0:c r="AL32" t="str">
+        <ns0:v>Новое</ns0:v>
+      </ns0:c>
+      <ns0:c r="AM32" t="inlineStr">
+        <ns0:is>
+          <ns0:t>В наличии</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="AN32" t="str">
+        <ns0:v>Отделка</ns0:v>
+      </ns0:c>
+      <ns0:c r="AO32"/>
+      <ns0:c r="AP32" t="str">
+        <ns0:v>Стеновые панели, рейки и элементы декора</ns0:v>
+      </ns0:c>
+      <ns0:c r="AQ32" t="str">
+        <ns0:v>Стеновые панели</ns0:v>
+      </ns0:c>
+      <ns0:c r="AR32" t="str">
+        <ns0:v>ПВХ</ns0:v>
+      </ns0:c>
+      <ns0:c r="AS32" t="str">
+        <ns0:v>Стены | Двери</ns0:v>
+      </ns0:c>
+      <ns0:c r="AT32" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AU32" t="n">
+        <ns0:v>2800</ns0:v>
+      </ns0:c>
+      <ns0:c r="AV32" t="n">
+        <ns0:v>1140</ns0:v>
+      </ns0:c>
+      <ns0:c r="AW32"/>
+      <ns0:c r="AX32" t="str">
+        <ns0:v>Нет</ns0:v>
+      </ns0:c>
+      <ns0:c r="AY32"/>
+      <ns0:c r="AZ32"/>
+      <ns0:c r="BA32"/>
+      <ns0:c r="BB32"/>
+      <ns0:c r="BC32"/>
+      <ns0:c r="BD32"/>
+      <ns0:c r="BE32"/>
+      <ns0:c r="BF32"/>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:dataValidations count="24">
     <ns0:dataValidation type="list" allowBlank="1" sqref="$D$5:$D$1048576">
